--- a/inventories/lci-Tr2050.xlsx
+++ b/inventories/lci-Tr2050.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joanna.schlesinger\0.Joanna\2. HySPI\ADEME_scenarios_premise\inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AB6699-6060-4CC3-AB5A-19744D2ED2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C6A939-99C3-4F15-BC92-E69198D11B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -341,10 +341,10 @@
     <t>market for electricity, high voltage</t>
   </si>
   <si>
+    <t>electricity production, from stationary battery, Tr2050</t>
+  </si>
+  <si>
     <t>Tr2050</t>
-  </si>
-  <si>
-    <t>electricity production, from stationary battery, Tr2050</t>
   </si>
 </sst>
 </file>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -2167,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C78" s="13"/>
       <c r="D78" s="9"/>

--- a/inventories/lci-Tr2050.xlsx
+++ b/inventories/lci-Tr2050.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joanna.schlesinger\0.Joanna\2. HySPI\ADEME_scenarios_premise\inventories\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jschlesinger\0.Joanna\2. HySPI\ADEME_scenarios_premise\inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020733DF-B953-436F-BEDB-05172F433018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DA717C-3527-4B78-8471-A05AD2896F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lci" sheetId="1" r:id="rId1"/>
@@ -2986,7 +2986,7 @@
         <v>108</v>
       </c>
       <c r="D109" s="43" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E109" s="43" t="s">
         <v>13</v>
@@ -4062,7 +4062,7 @@
         <v>108</v>
       </c>
       <c r="D157" s="43" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E157" s="43" t="s">
         <v>13</v>

--- a/inventories/lci-Tr2050.xlsx
+++ b/inventories/lci-Tr2050.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jschlesinger\0.Joanna\2. HySPI\ADEME_scenarios_premise\inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B9C03C-9654-4F5F-8953-3C09CC1C5D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1521C391-BCF6-4923-B754-ECBD64DA2349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lci" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="195">
   <si>
     <t>Database</t>
   </si>
@@ -571,6 +571,60 @@
   </si>
   <si>
     <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar, Tr2050</t>
+  </si>
+  <si>
+    <t>Activity adapted from the similar inventory provided by premise: change of the location of the electricity input &gt; FR</t>
+  </si>
+  <si>
+    <t>hydropower plant construction, reservoir, alpine region</t>
+  </si>
+  <si>
+    <t>hydropower plant, reservoir, alpine region</t>
+  </si>
+  <si>
+    <t>market for lubricating oil</t>
+  </si>
+  <si>
+    <t>lubricating oil</t>
+  </si>
+  <si>
+    <t>market for waste mineral oil</t>
+  </si>
+  <si>
+    <t>waste mineral oil</t>
+  </si>
+  <si>
+    <t>air::non-urban air or from high stacks</t>
+  </si>
+  <si>
+    <t>Methane, non-fossil</t>
+  </si>
+  <si>
+    <t>Occupation, lake, artificial</t>
+  </si>
+  <si>
+    <t>Transformation, from unspecified</t>
+  </si>
+  <si>
+    <t>square meter</t>
+  </si>
+  <si>
+    <t>Transformation, to industrial area</t>
+  </si>
+  <si>
+    <t>Transformation, to lake, artificial</t>
+  </si>
+  <si>
+    <t>Volume occupied, reservoir</t>
+  </si>
+  <si>
+    <t>cubic meter-year</t>
+  </si>
+  <si>
+    <t>Water, turbine use, unspecified natural origin</t>
+  </si>
+  <si>
+    <t>electricity production, hydro, pumped storage, Tr2050</t>
   </si>
 </sst>
 </file>
@@ -722,7 +776,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -779,6 +833,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Neutre" xfId="4" builtinId="28"/>
@@ -1063,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T141"/>
+  <dimension ref="A1:T166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.36328125" customWidth="1"/>
@@ -1283,7 +1339,7 @@
       <c r="N15" s="8"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" t="s">
+      <c r="A16" s="47" t="s">
         <v>98</v>
       </c>
       <c r="B16">
@@ -1311,7 +1367,7 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>80</v>
       </c>
@@ -1336,7 +1392,7 @@
       </c>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>83</v>
       </c>
@@ -1361,7 +1417,7 @@
       </c>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -1386,7 +1442,7 @@
       </c>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -1411,7 +1467,7 @@
       </c>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -1436,7 +1492,7 @@
       </c>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -1461,2646 +1517,3066 @@
       </c>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:11">
       <c r="B23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:11">
       <c r="B24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A25" s="24" t="s">
+    <row r="25" spans="1:11">
+      <c r="A25" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" s="26"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-    </row>
-    <row r="26" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A26" s="29" t="s">
+      <c r="B25" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="11"/>
+      <c r="K25" s="8"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="14">
         <v>1</v>
       </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-    </row>
-    <row r="27" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A27" s="29" t="s">
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="11"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
-    </row>
-    <row r="28" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A28" s="29" t="s">
+      <c r="B27" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="11"/>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
-    </row>
-    <row r="29" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A29" s="29" t="s">
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="11"/>
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-    </row>
-    <row r="30" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A30" s="29" t="s">
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="11"/>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28"/>
-    </row>
-    <row r="31" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A31" s="33" t="s">
+      <c r="B30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="17"/>
+      <c r="K30" s="8"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-    </row>
-    <row r="32" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A32" s="33" t="s">
+      <c r="B31" s="12"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="18"/>
+      <c r="K31" s="8"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" t="s">
         <v>6</v>
       </c>
-      <c r="E32" s="33" t="s">
+      <c r="E32" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="33" t="s">
+      <c r="H32" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="I32" s="33"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="33"/>
-      <c r="T32" s="34"/>
-    </row>
-    <row r="33" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A33" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" s="32">
+      <c r="J32" s="1"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="19">
         <v>1</v>
       </c>
-      <c r="C33" s="27" t="str">
+      <c r="C33" t="str">
         <f>B29</f>
         <v>FR</v>
       </c>
-      <c r="D33" s="27" t="str">
-        <f>B30</f>
+      <c r="D33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="13"/>
+      <c r="H33" s="18"/>
+      <c r="K33" s="8"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" s="19">
+        <v>4.0404040404040398E-13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" s="19">
+        <v>7.5599999999999996E-6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="19">
+        <v>-7.5599999999999996E-6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="19">
+        <v>1.25125</v>
+      </c>
+      <c r="C37" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="19">
+        <v>7.7000000000000001E-8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39" s="19">
+        <v>1.4E-5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="19">
+        <v>2.49876858810916E-4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" s="19">
+        <v>1.1580501231411899</v>
+      </c>
+      <c r="D41" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>186</v>
+      </c>
+      <c r="B42" s="19">
+        <v>3.4499999999999999E-3</v>
+      </c>
+      <c r="D42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>187</v>
+      </c>
+      <c r="B43" s="19">
+        <v>2.3E-5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>189</v>
+      </c>
+      <c r="B44" s="19">
+        <v>2.2999999999999999E-7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>190</v>
+      </c>
+      <c r="B45" s="19">
+        <v>2.2770000000000001E-5</v>
+      </c>
+      <c r="D45" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>191</v>
+      </c>
+      <c r="B46" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>192</v>
+      </c>
+      <c r="E46" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" s="19">
+        <v>1.1583000000000001</v>
+      </c>
+      <c r="D47" t="s">
+        <v>128</v>
+      </c>
+      <c r="E47" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="B48"/>
+      <c r="I48"/>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="B49"/>
+      <c r="I49"/>
+    </row>
+    <row r="50" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A50" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="26"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+    </row>
+    <row r="51" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A51" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="30">
+        <v>1</v>
+      </c>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+    </row>
+    <row r="52" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A52" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+    </row>
+    <row r="53" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A53" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="K53" s="28"/>
+      <c r="L53" s="28"/>
+      <c r="M53" s="28"/>
+      <c r="N53" s="28"/>
+      <c r="O53" s="28"/>
+      <c r="P53" s="28"/>
+    </row>
+    <row r="54" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A54" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
+      <c r="P54" s="28"/>
+    </row>
+    <row r="55" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A55" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" s="33"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="33"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="28"/>
+    </row>
+    <row r="56" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A56" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="25"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="28"/>
+      <c r="O56" s="28"/>
+      <c r="P56" s="28"/>
+    </row>
+    <row r="57" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A57" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="33"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
+      <c r="Q57" s="34"/>
+      <c r="R57" s="34"/>
+      <c r="S57" s="33"/>
+      <c r="T57" s="34"/>
+    </row>
+    <row r="58" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A58" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="32">
+        <v>1</v>
+      </c>
+      <c r="C58" s="27" t="str">
+        <f>B54</f>
+        <v>FR</v>
+      </c>
+      <c r="D58" s="27" t="str">
+        <f>B55</f>
         <v>kilogram</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="27" t="s">
+      <c r="E58" s="26"/>
+      <c r="F58" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G33" s="27" t="s">
+      <c r="G58" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
-      <c r="T33"/>
-    </row>
-    <row r="34" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A34" s="32" t="s">
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="T58"/>
+    </row>
+    <row r="59" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A59" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B59" s="27">
         <f>(1/2963200)*4</f>
         <v>1.3498920086393089E-6</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C59" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D59" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F34" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="27" t="s">
+      <c r="F59" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="H34" s="27" t="s">
+      <c r="H59" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="J34"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-    </row>
-    <row r="35" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A35" s="32" t="s">
+      <c r="J59"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36"/>
+      <c r="O59" s="36"/>
+      <c r="P59" s="36"/>
+      <c r="Q59"/>
+      <c r="R59"/>
+    </row>
+    <row r="60" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A60" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B60" s="27">
         <f>1/2963200</f>
         <v>3.3747300215982723E-7</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C60" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D60" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="27" t="s">
+      <c r="F60" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="H35" s="27" t="s">
+      <c r="H60" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="J35"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="36"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-    </row>
-    <row r="36" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A36" s="32" t="s">
+      <c r="J60"/>
+      <c r="K60" s="36"/>
+      <c r="L60" s="36"/>
+      <c r="M60" s="36"/>
+      <c r="N60" s="36"/>
+      <c r="O60" s="36"/>
+      <c r="P60" s="36"/>
+      <c r="Q60"/>
+      <c r="R60"/>
+    </row>
+    <row r="61" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A61" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="27">
-        <f>B34*-1</f>
+      <c r="B61" s="27">
+        <f>B59*-1</f>
         <v>-1.3498920086393089E-6</v>
       </c>
-      <c r="C36" s="27" t="s">
+      <c r="C61" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="27" t="s">
+      <c r="D61" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F36" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="27" t="s">
+      <c r="F61" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="H36" s="27" t="s">
+      <c r="H61" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="J36"/>
-      <c r="K36" s="36"/>
-      <c r="L36" s="36"/>
-      <c r="M36" s="36"/>
-      <c r="N36" s="36"/>
-      <c r="O36" s="36"/>
-      <c r="P36" s="36"/>
-      <c r="Q36"/>
-      <c r="R36"/>
-    </row>
-    <row r="37" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A37" s="32" t="s">
+      <c r="J61"/>
+      <c r="K61" s="36"/>
+      <c r="L61" s="36"/>
+      <c r="M61" s="36"/>
+      <c r="N61" s="36"/>
+      <c r="O61" s="36"/>
+      <c r="P61" s="36"/>
+      <c r="Q61"/>
+      <c r="R61"/>
+    </row>
+    <row r="62" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A62" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="27">
-        <f>-1*B35</f>
+      <c r="B62" s="27">
+        <f>-1*B60</f>
         <v>-3.3747300215982723E-7</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C62" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D62" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="27" t="s">
+      <c r="F62" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="H37" s="27" t="s">
+      <c r="H62" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="J37"/>
-      <c r="K37" s="36"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="36"/>
-      <c r="O37" s="36"/>
-      <c r="P37" s="36"/>
-      <c r="Q37"/>
-      <c r="R37"/>
-    </row>
-    <row r="38" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A38" s="29" t="s">
+      <c r="J62"/>
+      <c r="K62" s="36"/>
+      <c r="L62" s="36"/>
+      <c r="M62" s="36"/>
+      <c r="N62" s="36"/>
+      <c r="O62" s="36"/>
+      <c r="P62" s="36"/>
+      <c r="Q62"/>
+      <c r="R62"/>
+    </row>
+    <row r="63" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A63" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B63" s="32">
         <v>54</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C63" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D63" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="26"/>
-      <c r="F38" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="27" t="s">
+      <c r="E63" s="26"/>
+      <c r="F63" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="26" t="s">
+      <c r="H63" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="J38"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="36"/>
-      <c r="N38" s="36"/>
-      <c r="O38" s="36"/>
-      <c r="P38" s="36"/>
-      <c r="Q38"/>
-      <c r="R38"/>
-    </row>
-    <row r="39" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A39" s="29" t="s">
+      <c r="J63"/>
+      <c r="K63" s="36"/>
+      <c r="L63" s="36"/>
+      <c r="M63" s="36"/>
+      <c r="N63" s="36"/>
+      <c r="O63" s="36"/>
+      <c r="P63" s="36"/>
+      <c r="Q63"/>
+      <c r="R63"/>
+    </row>
+    <row r="64" spans="1:20" s="27" customFormat="1" ht="15.5">
+      <c r="A64" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B64" s="32">
         <v>14</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C64" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" s="27" t="s">
+      <c r="D64" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="H39" s="37" t="s">
+      <c r="H64" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="J39"/>
-      <c r="K39" s="36"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="36"/>
-      <c r="Q39"/>
-      <c r="R39"/>
-    </row>
-    <row r="40" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A40" s="38" t="s">
+      <c r="J64"/>
+      <c r="K64" s="36"/>
+      <c r="L64" s="36"/>
+      <c r="M64" s="36"/>
+      <c r="N64" s="36"/>
+      <c r="O64" s="36"/>
+      <c r="P64" s="36"/>
+      <c r="Q64"/>
+      <c r="R64"/>
+    </row>
+    <row r="65" spans="1:18" s="27" customFormat="1" ht="15.5">
+      <c r="A65" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B65" s="31">
         <v>8</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="38" t="s">
+      <c r="C65" s="38"/>
+      <c r="D65" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F40" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="38"/>
-      <c r="H40" s="39"/>
-      <c r="J40"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="36"/>
-      <c r="Q40" s="36"/>
-      <c r="R40"/>
-    </row>
-    <row r="41" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A41" s="38" t="s">
+      <c r="F65" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" s="38"/>
+      <c r="H65" s="39"/>
+      <c r="J65"/>
+      <c r="K65" s="36"/>
+      <c r="L65" s="36"/>
+      <c r="M65" s="36"/>
+      <c r="N65" s="36"/>
+      <c r="O65" s="36"/>
+      <c r="P65" s="36"/>
+      <c r="Q65" s="36"/>
+      <c r="R65"/>
+    </row>
+    <row r="66" spans="1:18" s="27" customFormat="1" ht="15.5">
+      <c r="A66" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="31">
+      <c r="B66" s="31">
         <f>(0.09*1000*20)/2963200</f>
         <v>6.0745140388768898E-4</v>
       </c>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38" t="s">
+      <c r="C66" s="38"/>
+      <c r="D66" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E41" s="38" t="s">
+      <c r="E66" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F41" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="38"/>
-      <c r="H41" s="39"/>
-      <c r="J41"/>
-      <c r="K41" s="36"/>
-      <c r="L41" s="36"/>
-      <c r="M41" s="36"/>
-      <c r="N41" s="36"/>
-      <c r="O41" s="36"/>
-      <c r="P41" s="36"/>
-      <c r="Q41" s="36"/>
-      <c r="R41"/>
-    </row>
-    <row r="42" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-    </row>
-    <row r="45" spans="1:20" ht="15.5">
-      <c r="A45" s="42" t="s">
+      <c r="F66" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" s="38"/>
+      <c r="H66" s="39"/>
+      <c r="J66"/>
+      <c r="K66" s="36"/>
+      <c r="L66" s="36"/>
+      <c r="M66" s="36"/>
+      <c r="N66" s="36"/>
+      <c r="O66" s="36"/>
+      <c r="P66" s="36"/>
+      <c r="Q66" s="36"/>
+      <c r="R66"/>
+    </row>
+    <row r="67" spans="1:18" s="27" customFormat="1" ht="15.5">
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+    </row>
+    <row r="70" spans="1:18" ht="15.5">
+      <c r="A70" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B45" s="42" t="s">
+      <c r="B70" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-    </row>
-    <row r="46" spans="1:20">
-      <c r="A46" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="B46" s="43">
-        <v>1.310870633</v>
-      </c>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-    </row>
-    <row r="47" spans="1:20">
-      <c r="A47" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="B47" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="43"/>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="A48" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-    </row>
-    <row r="51" spans="1:9" ht="15.5">
-      <c r="A51" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="43"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="43"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B52" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="E52" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53" s="43">
-        <v>1</v>
-      </c>
-      <c r="C53" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="43"/>
-      <c r="G53" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="H53" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="I53" s="43"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="B54" s="44">
-        <v>3.0676600000000002E-8</v>
-      </c>
-      <c r="C54" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G54" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" s="43"/>
-      <c r="I54" s="43"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="B55" s="44">
-        <v>4.6014800000000002E-6</v>
-      </c>
-      <c r="C55" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G55" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H55" s="43"/>
-      <c r="I55" s="43"/>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="B56" s="44">
-        <v>1.22709E-5</v>
-      </c>
-      <c r="C56" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G56" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" s="43"/>
-      <c r="I56" s="43"/>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="44">
-        <v>3.0676599999999998E-10</v>
-      </c>
-      <c r="C57" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H57" s="43"/>
-      <c r="I57" s="43"/>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58" s="44">
-        <v>2.1474199999999998E-5</v>
-      </c>
-      <c r="C58" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G58" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H58" s="43"/>
-      <c r="I58" s="43"/>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="43">
-        <v>8.9222937859999991</v>
-      </c>
-      <c r="C59" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D59" s="43"/>
-      <c r="E59" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G59" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" s="43"/>
-      <c r="I59" s="43"/>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B60" s="44">
-        <v>6.4421899999999994E-5</v>
-      </c>
-      <c r="C60" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D60" s="43"/>
-      <c r="E60" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G60" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" s="43"/>
-      <c r="I60" s="43"/>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B61" s="44">
-        <v>3.06766E-6</v>
-      </c>
-      <c r="C61" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D61" s="43"/>
-      <c r="E61" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G61" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="43"/>
-      <c r="I61" s="43"/>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B62" s="44">
-        <v>3.06766E-6</v>
-      </c>
-      <c r="C62" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D62" s="43"/>
-      <c r="E62" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H62" s="43"/>
-      <c r="I62" s="43"/>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B63" s="44">
-        <v>9.2032600000000003E-10</v>
-      </c>
-      <c r="C63" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D63" s="43"/>
-      <c r="E63" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H63" s="43"/>
-      <c r="I63" s="43"/>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B64" s="44">
-        <v>6.1356E-5</v>
-      </c>
-      <c r="C64" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D64" s="43"/>
-      <c r="E64" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H64" s="43"/>
-      <c r="I64" s="43"/>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="B65" s="43">
-        <v>5.4912400000000001E-4</v>
-      </c>
-      <c r="C65" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D65" s="43"/>
-      <c r="E65" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" s="43"/>
-      <c r="I65" s="43"/>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B66" s="44">
-        <v>3.0676599999999998E-7</v>
-      </c>
-      <c r="C66" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G66" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H66" s="43"/>
-      <c r="I66" s="43"/>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="B67" s="44">
-        <v>6.1356000000000002E-6</v>
-      </c>
-      <c r="C67" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D67" s="43"/>
-      <c r="E67" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G67" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" s="43"/>
-      <c r="I67" s="43"/>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B68" s="44">
-        <v>3.6814199999999997E-5</v>
-      </c>
-      <c r="C68" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D68" s="43"/>
-      <c r="E68" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G68" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="43"/>
-      <c r="I68" s="43"/>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B69" s="44">
-        <v>6.1356000000000002E-6</v>
-      </c>
-      <c r="C69" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" s="43"/>
-      <c r="I69" s="43"/>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="A70" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B70" s="44">
-        <v>6.1356E-7</v>
-      </c>
-      <c r="C70" s="43" t="s">
-        <v>109</v>
-      </c>
+      <c r="C70" s="43"/>
       <c r="D70" s="43"/>
-      <c r="E70" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G70" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E70" s="43"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="43"/>
       <c r="H70" s="43"/>
       <c r="I70" s="43"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:18">
       <c r="A71" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="B71" s="44">
-        <v>1.6872699999999999E-5</v>
-      </c>
-      <c r="C71" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B71" s="43">
+        <v>1.310870633</v>
+      </c>
+      <c r="C71" s="43"/>
       <c r="D71" s="43"/>
-      <c r="E71" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G71" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="43"/>
       <c r="H71" s="43"/>
       <c r="I71" s="43"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:18">
       <c r="A72" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B72" s="44">
-        <v>6.1356000000000002E-6</v>
-      </c>
-      <c r="C72" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B72" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="43"/>
       <c r="D72" s="43"/>
-      <c r="E72" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G72" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43"/>
       <c r="H72" s="43"/>
       <c r="I72" s="43"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:18">
       <c r="A73" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="B73" s="43">
-        <v>0.38040000000000002</v>
-      </c>
-      <c r="C73" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B73" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="43"/>
       <c r="D73" s="43"/>
-      <c r="E73" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F73" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="G73" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43"/>
       <c r="H73" s="43"/>
       <c r="I73" s="43"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:18">
       <c r="A74" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B74" s="43">
-        <v>0.37130000000000002</v>
-      </c>
-      <c r="C74" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B74" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="43"/>
       <c r="D74" s="43"/>
-      <c r="E74" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F74" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="G74" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E74" s="43"/>
+      <c r="F74" s="43"/>
+      <c r="G74" s="43"/>
       <c r="H74" s="43"/>
       <c r="I74" s="43"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:18">
       <c r="A75" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B75" s="43">
-        <v>9.1000000000000004E-3</v>
-      </c>
-      <c r="C75" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B75" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C75" s="43"/>
       <c r="D75" s="43"/>
-      <c r="E75" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F75" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G75" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E75" s="43"/>
+      <c r="F75" s="43"/>
+      <c r="G75" s="43"/>
       <c r="H75" s="43"/>
-      <c r="I75" s="43" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="B76" s="44">
-        <v>5.3483200000000002E-10</v>
-      </c>
-      <c r="C76" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D76" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E76" s="43" t="s">
+      <c r="I75" s="43"/>
+    </row>
+    <row r="76" spans="1:18" ht="15.5">
+      <c r="A76" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" s="43"/>
+      <c r="C76" s="43"/>
+      <c r="D76" s="43"/>
+      <c r="E76" s="43"/>
+      <c r="F76" s="43"/>
+      <c r="G76" s="43"/>
+      <c r="H76" s="43"/>
+      <c r="I76" s="43"/>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="A77" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D77" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="E77" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F76" s="43"/>
-      <c r="G76" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="I76" s="43"/>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="B77" s="43">
-        <v>5.32728E-4</v>
-      </c>
-      <c r="C77" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D77" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="E77" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="43"/>
+      <c r="F77" s="43" t="s">
+        <v>10</v>
+      </c>
       <c r="G77" s="43" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H77" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="I77" s="43"/>
-    </row>
-    <row r="78" spans="1:9">
+        <v>4</v>
+      </c>
+      <c r="I77" s="43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
       <c r="A78" s="43" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="B78" s="43">
-        <v>3.6000000000000001E-5</v>
+        <v>1</v>
       </c>
       <c r="C78" s="43" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="D78" s="43" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="E78" s="43" t="s">
         <v>13</v>
       </c>
       <c r="F78" s="43"/>
       <c r="G78" s="43" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H78" s="43" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="I78" s="43"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:18">
       <c r="A79" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="B79" s="43">
-        <v>3.6240000000000003E-4</v>
+        <v>108</v>
+      </c>
+      <c r="B79" s="44">
+        <v>3.0676600000000002E-8</v>
       </c>
       <c r="C79" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D79" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D79" s="43"/>
       <c r="E79" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F79" s="43"/>
+      <c r="F79" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G79" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H79" s="43" t="s">
-        <v>143</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H79" s="43"/>
       <c r="I79" s="43"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:18">
       <c r="A80" s="43" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="B80" s="44">
-        <v>2.54628E-9</v>
+        <v>4.6014800000000002E-6</v>
       </c>
       <c r="C80" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D80" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D80" s="43"/>
       <c r="E80" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F80" s="43"/>
+        <v>13</v>
+      </c>
+      <c r="F80" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G80" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H80" s="43" t="s">
-        <v>145</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H80" s="43"/>
       <c r="I80" s="43"/>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="B81" s="43">
-        <v>2.796E-5</v>
+        <v>111</v>
+      </c>
+      <c r="B81" s="44">
+        <v>1.22709E-5</v>
       </c>
       <c r="C81" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D81" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D81" s="43"/>
       <c r="E81" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F81" s="43"/>
+      <c r="F81" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G81" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H81" s="43" t="s">
-        <v>147</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H81" s="43"/>
       <c r="I81" s="43"/>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="43" t="s">
-        <v>148</v>
-      </c>
-      <c r="B82" s="43">
-        <v>1.668E-5</v>
+        <v>112</v>
+      </c>
+      <c r="B82" s="44">
+        <v>3.0676599999999998E-10</v>
       </c>
       <c r="C82" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D82" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D82" s="43"/>
       <c r="E82" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F82" s="43"/>
+      <c r="F82" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G82" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H82" s="43" t="s">
-        <v>149</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H82" s="43"/>
       <c r="I82" s="43"/>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="B83" s="43">
-        <v>2.0291999999999999E-4</v>
+        <v>113</v>
+      </c>
+      <c r="B83" s="44">
+        <v>2.1474199999999998E-5</v>
       </c>
       <c r="C83" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D83" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D83" s="43"/>
       <c r="E83" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F83" s="43"/>
+      <c r="F83" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G83" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H83" s="43" t="s">
-        <v>151</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H83" s="43"/>
       <c r="I83" s="43"/>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="43" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="B84" s="43">
-        <v>3.1236000000000002E-4</v>
+        <v>8.9222937859999991</v>
       </c>
       <c r="C84" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D84" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D84" s="43"/>
       <c r="E84" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F84" s="43"/>
+      <c r="F84" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G84" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H84" s="43" t="s">
-        <v>153</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H84" s="43"/>
       <c r="I84" s="43"/>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="B85" s="43">
-        <v>4.8000000000000001E-5</v>
+        <v>114</v>
+      </c>
+      <c r="B85" s="44">
+        <v>6.4421899999999994E-5</v>
       </c>
       <c r="C85" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D85" s="43" t="s">
-        <v>49</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D85" s="43"/>
       <c r="E85" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="43"/>
+      <c r="F85" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G85" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H85" s="43" t="s">
-        <v>155</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H85" s="43"/>
       <c r="I85" s="43"/>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="B86" s="43">
-        <v>1.1592E-5</v>
+        <v>115</v>
+      </c>
+      <c r="B86" s="44">
+        <v>3.06766E-6</v>
       </c>
       <c r="C86" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D86" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D86" s="43"/>
       <c r="E86" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F86" s="43"/>
+      <c r="F86" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G86" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H86" s="43" t="s">
-        <v>157</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H86" s="43"/>
       <c r="I86" s="43"/>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B87" s="43">
-        <v>7.538413555</v>
+        <v>116</v>
+      </c>
+      <c r="B87" s="44">
+        <v>3.06766E-6</v>
       </c>
       <c r="C87" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D87" s="43" t="s">
-        <v>22</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D87" s="43"/>
       <c r="E87" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="43"/>
+      <c r="F87" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G87" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H87" s="43" t="s">
-        <v>23</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H87" s="43"/>
       <c r="I87" s="43"/>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="B88" s="43">
-        <v>8.8290199999999997E-4</v>
+        <v>117</v>
+      </c>
+      <c r="B88" s="44">
+        <v>9.2032600000000003E-10</v>
       </c>
       <c r="C88" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D88" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D88" s="43"/>
       <c r="E88" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="43"/>
+      <c r="F88" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G88" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H88" s="43" t="s">
-        <v>159</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H88" s="43"/>
       <c r="I88" s="43"/>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="B89" s="43">
-        <v>3.7139999999999997E-4</v>
+        <v>118</v>
+      </c>
+      <c r="B89" s="44">
+        <v>6.1356E-5</v>
       </c>
       <c r="C89" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D89" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D89" s="43"/>
       <c r="E89" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F89" s="43"/>
+      <c r="F89" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G89" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H89" s="43" t="s">
-        <v>161</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H89" s="43"/>
       <c r="I89" s="43"/>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="43" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B90" s="43">
-        <v>0</v>
+        <v>5.4912400000000001E-4</v>
       </c>
       <c r="C90" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D90" s="43" t="s">
-        <v>29</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D90" s="43"/>
       <c r="E90" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90" s="43"/>
+        <v>13</v>
+      </c>
+      <c r="F90" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G90" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" s="43" t="s">
-        <v>31</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H90" s="43"/>
       <c r="I90" s="43"/>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="B91" s="43">
-        <v>4.3695687769999996</v>
+      <c r="A91" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B91" s="44">
+        <v>3.0676599999999998E-7</v>
       </c>
       <c r="C91" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D91" s="43" t="s">
-        <v>22</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D91" s="43"/>
       <c r="E91" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F91" s="43"/>
+        <v>13</v>
+      </c>
+      <c r="F91" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G91" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H91" s="43" t="s">
-        <v>163</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H91" s="43"/>
       <c r="I91" s="43"/>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="43"/>
-      <c r="B92" s="43"/>
-      <c r="C92" s="43"/>
+      <c r="A92" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="44">
+        <v>6.1356000000000002E-6</v>
+      </c>
+      <c r="C92" s="43" t="s">
+        <v>109</v>
+      </c>
       <c r="D92" s="43"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="43"/>
+      <c r="E92" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" s="43" t="s">
+        <v>15</v>
+      </c>
       <c r="H92" s="43"/>
       <c r="I92" s="43"/>
     </row>
-    <row r="93" spans="1:9" ht="15.5">
-      <c r="A93" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B93" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="C93" s="43"/>
+    <row r="93" spans="1:9">
+      <c r="A93" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="B93" s="44">
+        <v>3.6814199999999997E-5</v>
+      </c>
+      <c r="C93" s="43" t="s">
+        <v>109</v>
+      </c>
       <c r="D93" s="43"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="43"/>
-      <c r="G93" s="43"/>
+      <c r="E93" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G93" s="43" t="s">
+        <v>15</v>
+      </c>
       <c r="H93" s="43"/>
       <c r="I93" s="43"/>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="B94" s="43">
-        <v>1.290350439</v>
-      </c>
-      <c r="C94" s="43"/>
+        <v>123</v>
+      </c>
+      <c r="B94" s="44">
+        <v>6.1356000000000002E-6</v>
+      </c>
+      <c r="C94" s="43" t="s">
+        <v>109</v>
+      </c>
       <c r="D94" s="43"/>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="43"/>
+      <c r="E94" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="43" t="s">
+        <v>15</v>
+      </c>
       <c r="H94" s="43"/>
       <c r="I94" s="43"/>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="B95" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="C95" s="43"/>
+        <v>124</v>
+      </c>
+      <c r="B95" s="44">
+        <v>6.1356E-7</v>
+      </c>
+      <c r="C95" s="43" t="s">
+        <v>109</v>
+      </c>
       <c r="D95" s="43"/>
-      <c r="E95" s="43"/>
-      <c r="F95" s="43"/>
-      <c r="G95" s="43"/>
+      <c r="E95" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" s="43" t="s">
+        <v>15</v>
+      </c>
       <c r="H95" s="43"/>
       <c r="I95" s="43"/>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B96" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="C96" s="43"/>
+        <v>125</v>
+      </c>
+      <c r="B96" s="44">
+        <v>1.6872699999999999E-5</v>
+      </c>
+      <c r="C96" s="43" t="s">
+        <v>109</v>
+      </c>
       <c r="D96" s="43"/>
-      <c r="E96" s="43"/>
-      <c r="F96" s="43"/>
-      <c r="G96" s="43"/>
+      <c r="E96" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" s="43" t="s">
+        <v>15</v>
+      </c>
       <c r="H96" s="43"/>
       <c r="I96" s="43"/>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B97" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C97" s="43"/>
+        <v>126</v>
+      </c>
+      <c r="B97" s="44">
+        <v>6.1356000000000002E-6</v>
+      </c>
+      <c r="C97" s="43" t="s">
+        <v>109</v>
+      </c>
       <c r="D97" s="43"/>
-      <c r="E97" s="43"/>
-      <c r="F97" s="43"/>
-      <c r="G97" s="43"/>
+      <c r="E97" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" s="43" t="s">
+        <v>15</v>
+      </c>
       <c r="H97" s="43"/>
       <c r="I97" s="43"/>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="B98" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C98" s="43"/>
+        <v>127</v>
+      </c>
+      <c r="B98" s="43">
+        <v>0.38040000000000002</v>
+      </c>
+      <c r="C98" s="43" t="s">
+        <v>109</v>
+      </c>
       <c r="D98" s="43"/>
-      <c r="E98" s="43"/>
-      <c r="F98" s="43"/>
-      <c r="G98" s="43"/>
+      <c r="E98" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F98" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="G98" s="43" t="s">
+        <v>15</v>
+      </c>
       <c r="H98" s="43"/>
       <c r="I98" s="43"/>
     </row>
-    <row r="99" spans="1:9" ht="15.5">
-      <c r="A99" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="B99" s="43"/>
-      <c r="C99" s="43"/>
+    <row r="99" spans="1:9">
+      <c r="A99" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="B99" s="43">
+        <v>0.37130000000000002</v>
+      </c>
+      <c r="C99" s="43" t="s">
+        <v>109</v>
+      </c>
       <c r="D99" s="43"/>
-      <c r="E99" s="43"/>
-      <c r="F99" s="43"/>
-      <c r="G99" s="43"/>
+      <c r="E99" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F99" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G99" s="43" t="s">
+        <v>15</v>
+      </c>
       <c r="H99" s="43"/>
       <c r="I99" s="43"/>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B100" s="43" t="s">
-        <v>9</v>
+        <v>130</v>
+      </c>
+      <c r="B100" s="43">
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="C100" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D100" s="43" t="s">
-        <v>2</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D100" s="43"/>
       <c r="E100" s="43" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="F100" s="43" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G100" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="43" t="s">
-        <v>4</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H100" s="43"/>
       <c r="I100" s="43" t="s">
-        <v>11</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="B101" s="43">
-        <v>1</v>
+        <v>133</v>
+      </c>
+      <c r="B101" s="44">
+        <v>5.3483200000000002E-10</v>
       </c>
       <c r="C101" s="43" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="D101" s="43" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E101" s="43" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F101" s="43"/>
       <c r="G101" s="43" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H101" s="43" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="I101" s="43"/>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="B102" s="44">
-        <v>2.8033E-8</v>
+        <v>136</v>
+      </c>
+      <c r="B102" s="43">
+        <v>5.32728E-4</v>
       </c>
       <c r="C102" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D102" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D102" s="43" t="s">
+        <v>137</v>
+      </c>
       <c r="E102" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F102" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F102" s="43"/>
       <c r="G102" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H102" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H102" s="43" t="s">
+        <v>138</v>
+      </c>
       <c r="I102" s="43"/>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="B103" s="44">
-        <v>4.2049500000000003E-6</v>
+        <v>139</v>
+      </c>
+      <c r="B103" s="43">
+        <v>3.6000000000000001E-5</v>
       </c>
       <c r="C103" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D103" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D103" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E103" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F103" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F103" s="43"/>
       <c r="G103" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H103" s="43" t="s">
+        <v>141</v>
+      </c>
       <c r="I103" s="43"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="B104" s="44">
-        <v>1.12135E-5</v>
+        <v>142</v>
+      </c>
+      <c r="B104" s="43">
+        <v>3.6240000000000003E-4</v>
       </c>
       <c r="C104" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D104" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D104" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E104" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F104" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F104" s="43"/>
       <c r="G104" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H104" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H104" s="43" t="s">
+        <v>143</v>
+      </c>
       <c r="I104" s="43"/>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="43" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="B105" s="44">
-        <v>2.8033E-10</v>
+        <v>2.54628E-9</v>
       </c>
       <c r="C105" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D105" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D105" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E105" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" s="43" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F105" s="43"/>
       <c r="G105" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H105" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H105" s="43" t="s">
+        <v>145</v>
+      </c>
       <c r="I105" s="43"/>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="B106" s="44">
-        <v>1.96236E-5</v>
+        <v>146</v>
+      </c>
+      <c r="B106" s="43">
+        <v>2.796E-5</v>
       </c>
       <c r="C106" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D106" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D106" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E106" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F106" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F106" s="43"/>
       <c r="G106" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H106" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H106" s="43" t="s">
+        <v>147</v>
+      </c>
       <c r="I106" s="43"/>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="43" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="B107" s="43">
-        <v>2.6104586730000001</v>
+        <v>1.668E-5</v>
       </c>
       <c r="C107" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D107" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D107" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E107" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F107" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F107" s="43"/>
       <c r="G107" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H107" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H107" s="43" t="s">
+        <v>149</v>
+      </c>
       <c r="I107" s="43"/>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B108" s="44">
-        <v>5.8870399999999998E-5</v>
+        <v>150</v>
+      </c>
+      <c r="B108" s="43">
+        <v>2.0291999999999999E-4</v>
       </c>
       <c r="C108" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D108" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D108" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E108" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F108" s="43"/>
       <c r="G108" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H108" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H108" s="43" t="s">
+        <v>151</v>
+      </c>
       <c r="I108" s="43"/>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B109" s="44">
-        <v>2.8032999999999999E-6</v>
+        <v>152</v>
+      </c>
+      <c r="B109" s="43">
+        <v>3.1236000000000002E-4</v>
       </c>
       <c r="C109" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D109" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D109" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E109" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F109" s="43"/>
       <c r="G109" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H109" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H109" s="43" t="s">
+        <v>153</v>
+      </c>
       <c r="I109" s="43"/>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B110" s="44">
-        <v>2.8032999999999999E-6</v>
+        <v>154</v>
+      </c>
+      <c r="B110" s="43">
+        <v>4.8000000000000001E-5</v>
       </c>
       <c r="C110" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D110" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D110" s="43" t="s">
+        <v>49</v>
+      </c>
       <c r="E110" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F110" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F110" s="43"/>
       <c r="G110" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H110" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H110" s="43" t="s">
+        <v>155</v>
+      </c>
       <c r="I110" s="43"/>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B111" s="44">
-        <v>8.4101700000000003E-10</v>
+        <v>156</v>
+      </c>
+      <c r="B111" s="43">
+        <v>1.1592E-5</v>
       </c>
       <c r="C111" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D111" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D111" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E111" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F111" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F111" s="43"/>
       <c r="G111" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H111" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H111" s="43" t="s">
+        <v>157</v>
+      </c>
       <c r="I111" s="43"/>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B112" s="44">
-        <v>5.6068700000000001E-5</v>
+        <v>21</v>
+      </c>
+      <c r="B112" s="43">
+        <v>7.538413555</v>
       </c>
       <c r="C112" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D112" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D112" s="43" t="s">
+        <v>22</v>
+      </c>
       <c r="E112" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F112" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F112" s="43"/>
       <c r="G112" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H112" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H112" s="43" t="s">
+        <v>23</v>
+      </c>
       <c r="I112" s="43"/>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="43" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="B113" s="43">
-        <v>5.0180299999999999E-4</v>
+        <v>8.8290199999999997E-4</v>
       </c>
       <c r="C113" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D113" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D113" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E113" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F113" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F113" s="43"/>
       <c r="G113" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H113" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H113" s="43" t="s">
+        <v>159</v>
+      </c>
       <c r="I113" s="43"/>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B114" s="44">
-        <v>2.8033000000000002E-7</v>
+        <v>160</v>
+      </c>
+      <c r="B114" s="43">
+        <v>3.7139999999999997E-4</v>
       </c>
       <c r="C114" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D114" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D114" s="43" t="s">
+        <v>140</v>
+      </c>
       <c r="E114" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F114" s="43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F114" s="43"/>
       <c r="G114" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H114" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H114" s="43" t="s">
+        <v>161</v>
+      </c>
       <c r="I114" s="43"/>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="B115" s="44">
-        <v>5.6068700000000001E-6</v>
+        <v>98</v>
+      </c>
+      <c r="B115" s="43">
+        <v>0</v>
       </c>
       <c r="C115" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D115" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D115" s="43" t="s">
+        <v>29</v>
+      </c>
       <c r="E115" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" s="43" t="s">
-        <v>25</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F115" s="43"/>
       <c r="G115" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H115" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H115" s="43" t="s">
+        <v>31</v>
+      </c>
       <c r="I115" s="43"/>
     </row>
     <row r="116" spans="1:9">
-      <c r="A116" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B116" s="44">
-        <v>3.36417E-5</v>
+      <c r="A116" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="B116" s="43">
+        <v>4.3695687769999996</v>
       </c>
       <c r="C116" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D116" s="43"/>
+        <v>134</v>
+      </c>
+      <c r="D116" s="43" t="s">
+        <v>22</v>
+      </c>
       <c r="E116" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="43" t="s">
-        <v>25</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="F116" s="43"/>
       <c r="G116" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H116" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="H116" s="43" t="s">
+        <v>163</v>
+      </c>
       <c r="I116" s="43"/>
     </row>
     <row r="117" spans="1:9">
-      <c r="A117" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B117" s="44">
-        <v>5.6068700000000001E-6</v>
-      </c>
-      <c r="C117" s="43" t="s">
-        <v>109</v>
-      </c>
+      <c r="A117" s="43"/>
+      <c r="B117" s="43"/>
+      <c r="C117" s="43"/>
       <c r="D117" s="43"/>
-      <c r="E117" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F117" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G117" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E117" s="43"/>
+      <c r="F117" s="43"/>
+      <c r="G117" s="43"/>
       <c r="H117" s="43"/>
       <c r="I117" s="43"/>
     </row>
-    <row r="118" spans="1:9">
-      <c r="A118" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B118" s="44">
-        <v>5.6068700000000005E-7</v>
-      </c>
-      <c r="C118" s="43" t="s">
-        <v>109</v>
-      </c>
+    <row r="118" spans="1:9" ht="15.5">
+      <c r="A118" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B118" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="C118" s="43"/>
       <c r="D118" s="43"/>
-      <c r="E118" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G118" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E118" s="43"/>
+      <c r="F118" s="43"/>
+      <c r="G118" s="43"/>
       <c r="H118" s="43"/>
       <c r="I118" s="43"/>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="B119" s="44">
-        <v>1.5418699999999999E-5</v>
-      </c>
-      <c r="C119" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B119" s="43">
+        <v>1.290350439</v>
+      </c>
+      <c r="C119" s="43"/>
       <c r="D119" s="43"/>
-      <c r="E119" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G119" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E119" s="43"/>
+      <c r="F119" s="43"/>
+      <c r="G119" s="43"/>
       <c r="H119" s="43"/>
       <c r="I119" s="43"/>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B120" s="44">
-        <v>5.6068700000000001E-6</v>
-      </c>
-      <c r="C120" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B120" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120" s="43"/>
       <c r="D120" s="43"/>
-      <c r="E120" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F120" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G120" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E120" s="43"/>
+      <c r="F120" s="43"/>
+      <c r="G120" s="43"/>
       <c r="H120" s="43"/>
       <c r="I120" s="43"/>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="B121" s="43">
-        <v>0.38033800800000001</v>
-      </c>
-      <c r="C121" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B121" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="C121" s="43"/>
       <c r="D121" s="43"/>
-      <c r="E121" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F121" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="G121" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E121" s="43"/>
+      <c r="F121" s="43"/>
+      <c r="G121" s="43"/>
       <c r="H121" s="43"/>
       <c r="I121" s="43"/>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B122" s="43">
-        <v>0.36940000000000001</v>
-      </c>
-      <c r="C122" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B122" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C122" s="43"/>
       <c r="D122" s="43"/>
-      <c r="E122" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F122" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="G122" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E122" s="43"/>
+      <c r="F122" s="43"/>
+      <c r="G122" s="43"/>
       <c r="H122" s="43"/>
       <c r="I122" s="43"/>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B123" s="43">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="C123" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B123" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C123" s="43"/>
       <c r="D123" s="43"/>
-      <c r="E123" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F123" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G123" s="43" t="s">
-        <v>15</v>
-      </c>
+      <c r="E123" s="43"/>
+      <c r="F123" s="43"/>
+      <c r="G123" s="43"/>
       <c r="H123" s="43"/>
-      <c r="I123" s="43" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9">
-      <c r="A124" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="B124" s="43">
-        <v>6.1611670199999997</v>
-      </c>
-      <c r="C124" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D124" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E124" s="43" t="s">
-        <v>13</v>
-      </c>
+      <c r="I123" s="43"/>
+    </row>
+    <row r="124" spans="1:9" ht="15.5">
+      <c r="A124" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B124" s="43"/>
+      <c r="C124" s="43"/>
+      <c r="D124" s="43"/>
+      <c r="E124" s="43"/>
       <c r="F124" s="43"/>
-      <c r="G124" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H124" s="43" t="s">
-        <v>166</v>
-      </c>
+      <c r="G124" s="43"/>
+      <c r="H124" s="43"/>
       <c r="I124" s="43"/>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="B125" s="44">
-        <v>5.3477100000000001E-10</v>
+        <v>8</v>
+      </c>
+      <c r="B125" s="43" t="s">
+        <v>9</v>
       </c>
       <c r="C125" s="43" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="D125" s="43" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="E125" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F125" s="43"/>
+      <c r="F125" s="43" t="s">
+        <v>10</v>
+      </c>
       <c r="G125" s="43" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H125" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="I125" s="43"/>
+        <v>4</v>
+      </c>
+      <c r="I125" s="43" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="43" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="B126" s="43">
-        <v>5.32728E-4</v>
+        <v>1</v>
       </c>
       <c r="C126" s="43" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="D126" s="43" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="E126" s="43" t="s">
         <v>13</v>
       </c>
       <c r="F126" s="43"/>
       <c r="G126" s="43" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H126" s="43" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="I126" s="43"/>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="B127" s="43">
-        <v>3.6000000000000001E-5</v>
+        <v>108</v>
+      </c>
+      <c r="B127" s="44">
+        <v>2.8033E-8</v>
       </c>
       <c r="C127" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D127" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D127" s="43"/>
       <c r="E127" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F127" s="43"/>
+      <c r="F127" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G127" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H127" s="43" t="s">
-        <v>141</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H127" s="43"/>
       <c r="I127" s="43"/>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="B128" s="43">
-        <v>3.6240000000000003E-4</v>
+        <v>110</v>
+      </c>
+      <c r="B128" s="44">
+        <v>4.2049500000000003E-6</v>
       </c>
       <c r="C128" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D128" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D128" s="43"/>
       <c r="E128" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F128" s="43"/>
+      <c r="F128" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G128" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H128" s="43" t="s">
-        <v>143</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H128" s="43"/>
       <c r="I128" s="43"/>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="B129" s="43">
-        <v>2.0948000000000001E-4</v>
+        <v>111</v>
+      </c>
+      <c r="B129" s="44">
+        <v>1.12135E-5</v>
       </c>
       <c r="C129" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D129" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D129" s="43"/>
       <c r="E129" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F129" s="43"/>
+      <c r="F129" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G129" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H129" s="43" t="s">
-        <v>169</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H129" s="43"/>
       <c r="I129" s="43"/>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="43" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="B130" s="44">
-        <v>2.54628E-9</v>
+        <v>2.8033E-10</v>
       </c>
       <c r="C130" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D130" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D130" s="43"/>
       <c r="E130" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F130" s="43"/>
+        <v>13</v>
+      </c>
+      <c r="F130" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G130" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H130" s="43" t="s">
-        <v>145</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H130" s="43"/>
       <c r="I130" s="43"/>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="B131" s="43">
-        <v>2.796E-5</v>
+        <v>113</v>
+      </c>
+      <c r="B131" s="44">
+        <v>1.96236E-5</v>
       </c>
       <c r="C131" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D131" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D131" s="43"/>
       <c r="E131" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F131" s="43"/>
+      <c r="F131" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G131" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H131" s="43" t="s">
-        <v>147</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H131" s="43"/>
       <c r="I131" s="43"/>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="43" t="s">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="B132" s="43">
-        <v>1.668E-5</v>
+        <v>2.6104586730000001</v>
       </c>
       <c r="C132" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D132" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D132" s="43"/>
       <c r="E132" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F132" s="43"/>
+      <c r="F132" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G132" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H132" s="43" t="s">
-        <v>149</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H132" s="43"/>
       <c r="I132" s="43"/>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="B133" s="43">
-        <v>2.0291999999999999E-4</v>
+        <v>114</v>
+      </c>
+      <c r="B133" s="44">
+        <v>5.8870399999999998E-5</v>
       </c>
       <c r="C133" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D133" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D133" s="43"/>
       <c r="E133" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F133" s="43"/>
+      <c r="F133" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G133" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H133" s="43" t="s">
-        <v>151</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H133" s="43"/>
       <c r="I133" s="43"/>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="B134" s="43">
-        <v>3.1236000000000002E-4</v>
+        <v>115</v>
+      </c>
+      <c r="B134" s="44">
+        <v>2.8032999999999999E-6</v>
       </c>
       <c r="C134" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D134" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D134" s="43"/>
       <c r="E134" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F134" s="43"/>
+      <c r="F134" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G134" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H134" s="43" t="s">
-        <v>153</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H134" s="43"/>
       <c r="I134" s="43"/>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="B135" s="43">
-        <v>4.8000000000000001E-5</v>
+        <v>116</v>
+      </c>
+      <c r="B135" s="44">
+        <v>2.8032999999999999E-6</v>
       </c>
       <c r="C135" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D135" s="43" t="s">
-        <v>49</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D135" s="43"/>
       <c r="E135" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F135" s="43"/>
+      <c r="F135" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G135" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H135" s="43" t="s">
-        <v>155</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H135" s="43"/>
       <c r="I135" s="43"/>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="B136" s="43">
-        <v>1.1592E-5</v>
+        <v>117</v>
+      </c>
+      <c r="B136" s="44">
+        <v>8.4101700000000003E-10</v>
       </c>
       <c r="C136" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D136" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D136" s="43"/>
       <c r="E136" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F136" s="43"/>
+      <c r="F136" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G136" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H136" s="43" t="s">
-        <v>157</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H136" s="43"/>
       <c r="I136" s="43"/>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B137" s="43">
-        <v>7.5375498600000004</v>
+        <v>118</v>
+      </c>
+      <c r="B137" s="44">
+        <v>5.6068700000000001E-5</v>
       </c>
       <c r="C137" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D137" s="43" t="s">
-        <v>22</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D137" s="43"/>
       <c r="E137" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F137" s="43"/>
+      <c r="F137" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G137" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H137" s="43" t="s">
-        <v>23</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H137" s="43"/>
       <c r="I137" s="43"/>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="43" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="B138" s="43">
-        <v>8.8290199999999997E-4</v>
+        <v>5.0180299999999999E-4</v>
       </c>
       <c r="C138" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D138" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D138" s="43"/>
       <c r="E138" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F138" s="43"/>
+      <c r="F138" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G138" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H138" s="43" t="s">
-        <v>159</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H138" s="43"/>
       <c r="I138" s="43"/>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="B139" s="43">
-        <v>3.7139999999999997E-4</v>
+        <v>120</v>
+      </c>
+      <c r="B139" s="44">
+        <v>2.8033000000000002E-7</v>
       </c>
       <c r="C139" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D139" s="43" t="s">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D139" s="43"/>
       <c r="E139" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F139" s="43"/>
+      <c r="F139" s="43" t="s">
+        <v>25</v>
+      </c>
       <c r="G139" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H139" s="43" t="s">
-        <v>161</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H139" s="43"/>
       <c r="I139" s="43"/>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B140" s="44">
+        <v>5.6068700000000001E-6</v>
+      </c>
+      <c r="C140" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D140" s="43"/>
+      <c r="E140" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F140" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G140" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="43"/>
+      <c r="I140" s="43"/>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="B141" s="44">
+        <v>3.36417E-5</v>
+      </c>
+      <c r="C141" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D141" s="43"/>
+      <c r="E141" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G141" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" s="43"/>
+      <c r="I141" s="43"/>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B142" s="44">
+        <v>5.6068700000000001E-6</v>
+      </c>
+      <c r="C142" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D142" s="43"/>
+      <c r="E142" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F142" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G142" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" s="43"/>
+      <c r="I142" s="43"/>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B143" s="44">
+        <v>5.6068700000000005E-7</v>
+      </c>
+      <c r="C143" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D143" s="43"/>
+      <c r="E143" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G143" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" s="43"/>
+      <c r="I143" s="43"/>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B144" s="44">
+        <v>1.5418699999999999E-5</v>
+      </c>
+      <c r="C144" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D144" s="43"/>
+      <c r="E144" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G144" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" s="43"/>
+      <c r="I144" s="43"/>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B145" s="44">
+        <v>5.6068700000000001E-6</v>
+      </c>
+      <c r="C145" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D145" s="43"/>
+      <c r="E145" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G145" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" s="43"/>
+      <c r="I145" s="43"/>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B146" s="43">
+        <v>0.38033800800000001</v>
+      </c>
+      <c r="C146" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D146" s="43"/>
+      <c r="E146" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F146" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="G146" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" s="43"/>
+      <c r="I146" s="43"/>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="B147" s="43">
+        <v>0.36940000000000001</v>
+      </c>
+      <c r="C147" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D147" s="43"/>
+      <c r="E147" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F147" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G147" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" s="43"/>
+      <c r="I147" s="43"/>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="B148" s="43">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="C148" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D148" s="43"/>
+      <c r="E148" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F148" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G148" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" s="43"/>
+      <c r="I148" s="43" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="B149" s="43">
+        <v>6.1611670199999997</v>
+      </c>
+      <c r="C149" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D149" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E149" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" s="43"/>
+      <c r="G149" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H149" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="I149" s="43"/>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B150" s="44">
+        <v>5.3477100000000001E-10</v>
+      </c>
+      <c r="C150" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D150" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E150" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="F150" s="43"/>
+      <c r="G150" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H150" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="I150" s="43"/>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="B151" s="43">
+        <v>5.32728E-4</v>
+      </c>
+      <c r="C151" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D151" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E151" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="43"/>
+      <c r="G151" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H151" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="I151" s="43"/>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="B152" s="43">
+        <v>3.6000000000000001E-5</v>
+      </c>
+      <c r="C152" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D152" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E152" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="43"/>
+      <c r="G152" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H152" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="I152" s="43"/>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="B153" s="43">
+        <v>3.6240000000000003E-4</v>
+      </c>
+      <c r="C153" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D153" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E153" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="43"/>
+      <c r="G153" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H153" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="I153" s="43"/>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="B154" s="43">
+        <v>2.0948000000000001E-4</v>
+      </c>
+      <c r="C154" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D154" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E154" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="43"/>
+      <c r="G154" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H154" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I154" s="43"/>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B155" s="44">
+        <v>2.54628E-9</v>
+      </c>
+      <c r="C155" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D155" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E155" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="F155" s="43"/>
+      <c r="G155" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H155" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="I155" s="43"/>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="B156" s="43">
+        <v>2.796E-5</v>
+      </c>
+      <c r="C156" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D156" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E156" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="43"/>
+      <c r="G156" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H156" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="I156" s="43"/>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B157" s="43">
+        <v>1.668E-5</v>
+      </c>
+      <c r="C157" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D157" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E157" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="43"/>
+      <c r="G157" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H157" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="I157" s="43"/>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="B158" s="43">
+        <v>2.0291999999999999E-4</v>
+      </c>
+      <c r="C158" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D158" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E158" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="43"/>
+      <c r="G158" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H158" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="I158" s="43"/>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="B159" s="43">
+        <v>3.1236000000000002E-4</v>
+      </c>
+      <c r="C159" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D159" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E159" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="43"/>
+      <c r="G159" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H159" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="I159" s="43"/>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="B160" s="43">
+        <v>4.8000000000000001E-5</v>
+      </c>
+      <c r="C160" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D160" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E160" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="43"/>
+      <c r="G160" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H160" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="I160" s="43"/>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="B161" s="43">
+        <v>1.1592E-5</v>
+      </c>
+      <c r="C161" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D161" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E161" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="43"/>
+      <c r="G161" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H161" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="I161" s="43"/>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B162" s="43">
+        <v>7.5375498600000004</v>
+      </c>
+      <c r="C162" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D162" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E162" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" s="43"/>
+      <c r="G162" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H162" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="I162" s="43"/>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="B163" s="43">
+        <v>8.8290199999999997E-4</v>
+      </c>
+      <c r="C163" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D163" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E163" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="43"/>
+      <c r="G163" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H163" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="I163" s="43"/>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="B164" s="43">
+        <v>3.7139999999999997E-4</v>
+      </c>
+      <c r="C164" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D164" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E164" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="43"/>
+      <c r="G164" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H164" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="I164" s="43"/>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="B140" s="43">
+      <c r="B165" s="43">
         <v>0</v>
       </c>
-      <c r="C140" s="43" t="s">
+      <c r="C165" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="D140" s="43" t="s">
+      <c r="D165" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E140" s="43" t="s">
+      <c r="E165" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="F140" s="43"/>
-      <c r="G140" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H140" s="43" t="s">
+      <c r="F165" s="43"/>
+      <c r="G165" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H165" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="I140" s="43"/>
-    </row>
-    <row r="141" spans="1:9">
-      <c r="A141" s="45" t="s">
+      <c r="I165" s="43"/>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="B141" s="43">
+      <c r="B166" s="43">
         <v>4.3011681309999998</v>
       </c>
-      <c r="C141" s="43" t="s">
+      <c r="C166" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="D141" s="43" t="s">
+      <c r="D166" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="E141" s="43" t="s">
+      <c r="E166" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="F141" s="43"/>
-      <c r="G141" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H141" s="43" t="s">
+      <c r="F166" s="43"/>
+      <c r="G166" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H166" s="43" t="s">
         <v>163</v>
       </c>
-      <c r="I141" s="43"/>
+      <c r="I166" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inventories/lci-Tr2050.xlsx
+++ b/inventories/lci-Tr2050.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jschlesinger\0.Joanna\2. HySPI\ADEME_scenarios_premise\inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1521C391-BCF6-4923-B754-ECBD64DA2349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46D53F0-D429-4579-B7F6-F2E75EEE23EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lci" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="198">
   <si>
     <t>Database</t>
   </si>
@@ -625,6 +625,15 @@
   </si>
   <si>
     <t>electricity production, hydro, pumped storage, Tr2050</t>
+  </si>
+  <si>
+    <t>nothing</t>
+  </si>
+  <si>
+    <t>empty activity, for market that does not exist any more in 2050, Tr2050</t>
+  </si>
+  <si>
+    <t>used for market for hydrogen, for fossil fuel refinery in 2050 as this market does not exist anymore in 2050</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T166"/>
+  <dimension ref="A1:T185"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.36328125" customWidth="1"/>
@@ -4578,6 +4587,144 @@
       </c>
       <c r="I166" s="43"/>
     </row>
+    <row r="168" spans="1:9" ht="15.5">
+      <c r="A168" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B168" s="34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>2</v>
+      </c>
+      <c r="B169" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>11</v>
+      </c>
+      <c r="B170" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" t="s">
+        <v>3</v>
+      </c>
+      <c r="B171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" t="s">
+        <v>76</v>
+      </c>
+      <c r="B172"/>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" t="s">
+        <v>4</v>
+      </c>
+      <c r="B173" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" t="s">
+        <v>5</v>
+      </c>
+      <c r="B174" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" t="s">
+        <v>6</v>
+      </c>
+      <c r="B175" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="15.5">
+      <c r="A176" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B176"/>
+    </row>
+    <row r="177" spans="1:8" ht="15.5">
+      <c r="A177" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D177" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E177" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F177" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="G177" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H177" s="34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" t="str">
+        <f>B168</f>
+        <v>empty activity, for market that does not exist any more in 2050, Tr2050</v>
+      </c>
+      <c r="B178">
+        <v>1</v>
+      </c>
+      <c r="C178" t="s">
+        <v>29</v>
+      </c>
+      <c r="D178" t="str">
+        <f>B175</f>
+        <v>kilogram</v>
+      </c>
+      <c r="F178" t="s">
+        <v>18</v>
+      </c>
+      <c r="G178" t="str">
+        <f>B173</f>
+        <v>nothing</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="B179"/>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="B180" s="41"/>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="B181" s="41"/>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="B182" s="41"/>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="B183"/>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="B184"/>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="B185"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/inventories/lci-Tr2050.xlsx
+++ b/inventories/lci-Tr2050.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jschlesinger\0.Joanna\2. HySPI\ADEME_scenarios_premise\inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46D53F0-D429-4579-B7F6-F2E75EEE23EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E18D1B-4BB5-4CBC-8B72-ECD349E20320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="133">
   <si>
     <t>Database</t>
   </si>
@@ -348,84 +348,9 @@
     <t>electricity production, from hydrogen, Tr2050</t>
   </si>
   <si>
-    <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
-  </si>
-  <si>
-    <t>Total energy input to reformer</t>
-  </si>
-  <si>
-    <t>hydrogen, gaseous, 25 bar</t>
-  </si>
-  <si>
-    <t>Natural gas:  0.735 kg/m3 at standard condition @ 15°C, 1.0325 bar. LHV by mass: 46.5 MJ/kg. LHV by volume at standard condition: 36.0 MJ/Nm3.</t>
-  </si>
-  <si>
-    <t>database</t>
-  </si>
-  <si>
-    <t>Car db</t>
-  </si>
-  <si>
-    <t>Acetaldehyde</t>
-  </si>
-  <si>
-    <t>biosphere3</t>
-  </si>
-  <si>
-    <t>Acetic acid</t>
-  </si>
-  <si>
-    <t>Benzene</t>
-  </si>
-  <si>
-    <t>Benzo(a)pyrene</t>
-  </si>
-  <si>
-    <t>Butane</t>
-  </si>
-  <si>
-    <t>Carbon monoxide, fossil</t>
-  </si>
-  <si>
     <t>Dinitrogen monoxide</t>
   </si>
   <si>
-    <t>Formaldehyde</t>
-  </si>
-  <si>
-    <t>Mercury</t>
-  </si>
-  <si>
-    <t>Methane, fossil</t>
-  </si>
-  <si>
-    <t>Nitrogen oxides</t>
-  </si>
-  <si>
-    <t>PAH, polycyclic aromatic hydrocarbons</t>
-  </si>
-  <si>
-    <t>Particulates, &lt; 2.5 um</t>
-  </si>
-  <si>
-    <t>Pentane</t>
-  </si>
-  <si>
-    <t>Propane</t>
-  </si>
-  <si>
-    <t>Propionic acid</t>
-  </si>
-  <si>
-    <t>Sulfur dioxide</t>
-  </si>
-  <si>
-    <t>Toluene</t>
-  </si>
-  <si>
-    <t>Water, cooling, unspecified natural origin</t>
-  </si>
-  <si>
     <t>cubic meter</t>
   </si>
   <si>
@@ -438,120 +363,6 @@
     <t>water</t>
   </si>
   <si>
-    <t>Assumed 2.4 gallons (9.1 liters) of evaporated water per kg H2, according to https://www.hydrogen.energy.gov/docs/hydrogenprogramlibraries/pdfs/review16/sa039_elgowainy_2016_o.pdf?Status=Master</t>
-  </si>
-  <si>
-    <t>chemical factory construction, organics</t>
-  </si>
-  <si>
-    <t>ecoinvent 3.5 cutoff</t>
-  </si>
-  <si>
-    <t>chemical factory, organics</t>
-  </si>
-  <si>
-    <t>market for aluminium oxide, metallurgical</t>
-  </si>
-  <si>
-    <t>IAI Area, EU27 &amp; EFTA</t>
-  </si>
-  <si>
-    <t>aluminium oxide, metallurgical</t>
-  </si>
-  <si>
-    <t>market for chromium oxide, flakes</t>
-  </si>
-  <si>
-    <t>GLO</t>
-  </si>
-  <si>
-    <t>chromium oxide, flakes</t>
-  </si>
-  <si>
-    <t>market for copper oxide</t>
-  </si>
-  <si>
-    <t>copper oxide</t>
-  </si>
-  <si>
-    <t>market for liquid storage tank, chemicals, organics</t>
-  </si>
-  <si>
-    <t>liquid storage tank, chemicals, organics</t>
-  </si>
-  <si>
-    <t>market for magnesium oxide</t>
-  </si>
-  <si>
-    <t>magnesium oxide</t>
-  </si>
-  <si>
-    <t>market for molybdenum trioxide</t>
-  </si>
-  <si>
-    <t>molybdenum trioxide</t>
-  </si>
-  <si>
-    <t>market for nickel, class 1</t>
-  </si>
-  <si>
-    <t>nickel, class 1</t>
-  </si>
-  <si>
-    <t>market for portafer</t>
-  </si>
-  <si>
-    <t>portafer</t>
-  </si>
-  <si>
-    <t>market for quicklime, milled, packed</t>
-  </si>
-  <si>
-    <t>quicklime, milled, packed</t>
-  </si>
-  <si>
-    <t>market for silica sand</t>
-  </si>
-  <si>
-    <t>silica sand</t>
-  </si>
-  <si>
-    <t>market for zeolite, powder</t>
-  </si>
-  <si>
-    <t>zeolite, powder</t>
-  </si>
-  <si>
-    <t>market for zinc oxide</t>
-  </si>
-  <si>
-    <t>zinc oxide</t>
-  </si>
-  <si>
-    <t>market group for natural gas, high pressure</t>
-  </si>
-  <si>
-    <t>natural gas, high pressure</t>
-  </si>
-  <si>
-    <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
-  </si>
-  <si>
-    <t>Assumed 2.9 gallons (11 liters) of evaporated water per kg H2, according to https://www.hydrogen.energy.gov/docs/hydrogenprogramlibraries/pdfs/review16/sa039_elgowainy_2016_o.pdf?Status=Master</t>
-  </si>
-  <si>
-    <t>carbon dioxide, captured at hydrogen production plant, pre, pipeline 200km, storage 1000m</t>
-  </si>
-  <si>
-    <t>ecoinvent 3.6 cutoff</t>
-  </si>
-  <si>
-    <t>market for diethanolamine</t>
-  </si>
-  <si>
-    <t>diethanolamine</t>
-  </si>
-  <si>
     <t>hydrogen, recovered from coke oven gas, with carbon capture and storage</t>
   </si>
   <si>
@@ -565,12 +376,6 @@
   </si>
   <si>
     <t>skip</t>
-  </si>
-  <si>
-    <t>hydrogen production, steam methane reforming of natural gas, 25 bar, Tr2050</t>
-  </si>
-  <si>
-    <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar, Tr2050</t>
   </si>
   <si>
     <t>Activity adapted from the similar inventory provided by premise: change of the location of the electricity input &gt; FR</t>
@@ -643,7 +448,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -726,14 +531,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -785,7 +582,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -839,11 +636,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Neutre" xfId="4" builtinId="28"/>
@@ -1128,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T185"/>
+  <dimension ref="A1:T88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.36328125" customWidth="1"/>
@@ -1196,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="I5"/>
       <c r="M5" t="s">
@@ -1348,13 +1144,13 @@
       <c r="N15" s="8"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="44" t="s">
         <v>98</v>
       </c>
       <c r="B16">
         <v>1.33</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="44" t="s">
         <v>29</v>
       </c>
       <c r="D16" t="s">
@@ -1538,8 +1334,8 @@
       <c r="A25" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="46" t="s">
-        <v>194</v>
+      <c r="B25" s="43" t="s">
+        <v>129</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="9"/>
@@ -1571,7 +1367,7 @@
         <v>11</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -1674,7 +1470,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="19" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="B33" s="19">
         <v>1</v>
@@ -1698,7 +1494,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="B34" s="19">
         <v>4.0404040404040398E-13</v>
@@ -1713,12 +1509,12 @@
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="B35" s="19">
         <v>7.5599999999999996E-6</v>
@@ -1733,12 +1529,12 @@
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="B36" s="19">
         <v>-7.5599999999999996E-6</v>
@@ -1753,17 +1549,17 @@
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" t="s">
+      <c r="A37" s="44" t="s">
         <v>98</v>
       </c>
       <c r="B37" s="19">
         <v>1.25125</v>
       </c>
-      <c r="C37" s="47" t="s">
+      <c r="C37" s="44" t="s">
         <v>29</v>
       </c>
       <c r="D37" t="s">
@@ -1778,7 +1574,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B38" s="19">
         <v>7.7000000000000001E-8</v>
@@ -1790,12 +1586,12 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>184</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="B39" s="19">
         <v>1.4E-5</v>
@@ -1807,18 +1603,18 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>184</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="B40" s="19">
         <v>2.49876858810916E-4</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -1829,24 +1625,24 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="B41" s="19">
         <v>1.1580501231411899</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="B42" s="19">
         <v>3.4499999999999999E-3</v>
@@ -1863,13 +1659,13 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="B43" s="19">
         <v>2.3E-5</v>
       </c>
       <c r="D43" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -1880,13 +1676,13 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="B44" s="19">
         <v>2.2999999999999999E-7</v>
       </c>
       <c r="D44" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -1897,13 +1693,13 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="B45" s="19">
         <v>2.2770000000000001E-5</v>
       </c>
       <c r="D45" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -1914,36 +1710,36 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="B46" s="19">
         <v>0.15</v>
       </c>
       <c r="D46" t="s">
-        <v>192</v>
+        <v>127</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="B47" s="19">
         <v>1.1583000000000001</v>
       </c>
       <c r="D47" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -1959,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="C50" s="26"/>
       <c r="K50" s="28"/>
@@ -2265,13 +2061,13 @@
       <c r="R62"/>
     </row>
     <row r="63" spans="1:20" s="27" customFormat="1" ht="15.5">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="45" t="s">
         <v>28</v>
       </c>
       <c r="B63" s="32">
         <v>54</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="C63" s="46" t="s">
         <v>29</v>
       </c>
       <c r="D63" s="27" t="s">
@@ -2396,2334 +2192,154 @@
       <c r="O67" s="28"/>
       <c r="P67" s="28"/>
     </row>
-    <row r="70" spans="1:18" ht="15.5">
-      <c r="A70" s="42" t="s">
+    <row r="69" spans="1:18">
+      <c r="A69" s="42"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+      <c r="I69" s="42"/>
+    </row>
+    <row r="71" spans="1:18" ht="15.5">
+      <c r="A71" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B70" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="C70" s="43"/>
-      <c r="D70" s="43"/>
-      <c r="E70" s="43"/>
-      <c r="F70" s="43"/>
-      <c r="G70" s="43"/>
-      <c r="H70" s="43"/>
-      <c r="I70" s="43"/>
-    </row>
-    <row r="71" spans="1:18">
-      <c r="A71" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="B71" s="43">
-        <v>1.310870633</v>
-      </c>
-      <c r="C71" s="43"/>
-      <c r="D71" s="43"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="43"/>
-      <c r="H71" s="43"/>
-      <c r="I71" s="43"/>
+      <c r="B71" s="34" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="43" t="s">
+      <c r="A72" t="s">
         <v>2</v>
       </c>
-      <c r="B72" s="43" t="s">
+      <c r="B72" t="s">
         <v>29</v>
       </c>
-      <c r="C72" s="43"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="43"/>
-      <c r="H72" s="43"/>
-      <c r="I72" s="43"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="43" t="s">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="A74" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75"/>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="A76" t="s">
         <v>4</v>
       </c>
-      <c r="B73" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" s="43"/>
-      <c r="D73" s="43"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
-      <c r="G73" s="43"/>
-      <c r="H73" s="43"/>
-      <c r="I73" s="43"/>
-    </row>
-    <row r="74" spans="1:18">
-      <c r="A74" s="43" t="s">
+      <c r="B76" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="A77" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
+      <c r="A78" t="s">
         <v>6</v>
       </c>
-      <c r="B74" s="43" t="s">
+      <c r="B78" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C74" s="43"/>
-      <c r="D74" s="43"/>
-      <c r="E74" s="43"/>
-      <c r="F74" s="43"/>
-      <c r="G74" s="43"/>
-      <c r="H74" s="43"/>
-      <c r="I74" s="43"/>
-    </row>
-    <row r="75" spans="1:18">
-      <c r="A75" s="43" t="s">
+    </row>
+    <row r="79" spans="1:18" ht="15.5">
+      <c r="A79" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79"/>
+    </row>
+    <row r="80" spans="1:18" ht="15.5">
+      <c r="A80" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E80" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H80" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C75" s="43"/>
-      <c r="D75" s="43"/>
-      <c r="E75" s="43"/>
-      <c r="F75" s="43"/>
-      <c r="G75" s="43"/>
-      <c r="H75" s="43"/>
-      <c r="I75" s="43"/>
-    </row>
-    <row r="76" spans="1:18" ht="15.5">
-      <c r="A76" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" s="43"/>
-      <c r="C76" s="43"/>
-      <c r="D76" s="43"/>
-      <c r="E76" s="43"/>
-      <c r="F76" s="43"/>
-      <c r="G76" s="43"/>
-      <c r="H76" s="43"/>
-      <c r="I76" s="43"/>
-    </row>
-    <row r="77" spans="1:18">
-      <c r="A77" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B77" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C77" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D77" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="E77" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F77" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G77" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="H77" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I77" s="43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18">
-      <c r="A78" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B78" s="43">
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="str">
+        <f>B71</f>
+        <v>empty activity, for market that does not exist any more in 2050, Tr2050</v>
+      </c>
+      <c r="B81">
         <v>1</v>
       </c>
-      <c r="C78" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D78" s="43" t="s">
+      <c r="C81" t="s">
         <v>29</v>
       </c>
-      <c r="E78" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="43"/>
-      <c r="G78" s="43" t="s">
+      <c r="D81" t="str">
+        <f>B78</f>
+        <v>kilogram</v>
+      </c>
+      <c r="F81" t="s">
         <v>18</v>
       </c>
-      <c r="H78" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="I78" s="43"/>
-    </row>
-    <row r="79" spans="1:18">
-      <c r="A79" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="B79" s="44">
-        <v>3.0676600000000002E-8</v>
-      </c>
-      <c r="C79" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D79" s="43"/>
-      <c r="E79" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" s="43"/>
-      <c r="I79" s="43"/>
-    </row>
-    <row r="80" spans="1:18">
-      <c r="A80" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="B80" s="44">
-        <v>4.6014800000000002E-6</v>
-      </c>
-      <c r="C80" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D80" s="43"/>
-      <c r="E80" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G80" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="43"/>
-      <c r="I80" s="43"/>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="B81" s="44">
-        <v>1.22709E-5</v>
-      </c>
-      <c r="C81" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D81" s="43"/>
-      <c r="E81" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H81" s="43"/>
-      <c r="I81" s="43"/>
-    </row>
-    <row r="82" spans="1:9">
-      <c r="A82" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="B82" s="44">
-        <v>3.0676599999999998E-10</v>
-      </c>
-      <c r="C82" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G82" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H82" s="43"/>
-      <c r="I82" s="43"/>
-    </row>
-    <row r="83" spans="1:9">
-      <c r="A83" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="B83" s="44">
-        <v>2.1474199999999998E-5</v>
-      </c>
-      <c r="C83" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D83" s="43"/>
-      <c r="E83" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G83" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H83" s="43"/>
-      <c r="I83" s="43"/>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B84" s="43">
-        <v>8.9222937859999991</v>
-      </c>
-      <c r="C84" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D84" s="43"/>
-      <c r="E84" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G84" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="43"/>
-      <c r="I84" s="43"/>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B85" s="44">
-        <v>6.4421899999999994E-5</v>
-      </c>
-      <c r="C85" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D85" s="43"/>
-      <c r="E85" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G85" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H85" s="43"/>
-      <c r="I85" s="43"/>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B86" s="44">
-        <v>3.06766E-6</v>
-      </c>
-      <c r="C86" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D86" s="43"/>
-      <c r="E86" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G86" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H86" s="43"/>
-      <c r="I86" s="43"/>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B87" s="44">
-        <v>3.06766E-6</v>
-      </c>
-      <c r="C87" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D87" s="43"/>
-      <c r="E87" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G87" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H87" s="43"/>
-      <c r="I87" s="43"/>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B88" s="44">
-        <v>9.2032600000000003E-10</v>
-      </c>
-      <c r="C88" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D88" s="43"/>
-      <c r="E88" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G88" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="43"/>
-      <c r="I88" s="43"/>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B89" s="44">
-        <v>6.1356E-5</v>
-      </c>
-      <c r="C89" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D89" s="43"/>
-      <c r="E89" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G89" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H89" s="43"/>
-      <c r="I89" s="43"/>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="B90" s="43">
-        <v>5.4912400000000001E-4</v>
-      </c>
-      <c r="C90" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D90" s="43"/>
-      <c r="E90" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G90" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" s="43"/>
-      <c r="I90" s="43"/>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B91" s="44">
-        <v>3.0676599999999998E-7</v>
-      </c>
-      <c r="C91" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D91" s="43"/>
-      <c r="E91" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G91" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H91" s="43"/>
-      <c r="I91" s="43"/>
-    </row>
-    <row r="92" spans="1:9">
-      <c r="A92" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="B92" s="44">
-        <v>6.1356000000000002E-6</v>
-      </c>
-      <c r="C92" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D92" s="43"/>
-      <c r="E92" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G92" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H92" s="43"/>
-      <c r="I92" s="43"/>
-    </row>
-    <row r="93" spans="1:9">
-      <c r="A93" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B93" s="44">
-        <v>3.6814199999999997E-5</v>
-      </c>
-      <c r="C93" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D93" s="43"/>
-      <c r="E93" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G93" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" s="43"/>
-      <c r="I93" s="43"/>
-    </row>
-    <row r="94" spans="1:9">
-      <c r="A94" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B94" s="44">
-        <v>6.1356000000000002E-6</v>
-      </c>
-      <c r="C94" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D94" s="43"/>
-      <c r="E94" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" s="43"/>
-      <c r="I94" s="43"/>
-    </row>
-    <row r="95" spans="1:9">
-      <c r="A95" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B95" s="44">
-        <v>6.1356E-7</v>
-      </c>
-      <c r="C95" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D95" s="43"/>
-      <c r="E95" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G95" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" s="43"/>
-      <c r="I95" s="43"/>
-    </row>
-    <row r="96" spans="1:9">
-      <c r="A96" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="B96" s="44">
-        <v>1.6872699999999999E-5</v>
-      </c>
-      <c r="C96" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D96" s="43"/>
-      <c r="E96" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F96" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G96" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H96" s="43"/>
-      <c r="I96" s="43"/>
-    </row>
-    <row r="97" spans="1:9">
-      <c r="A97" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B97" s="44">
-        <v>6.1356000000000002E-6</v>
-      </c>
-      <c r="C97" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D97" s="43"/>
-      <c r="E97" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G97" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H97" s="43"/>
-      <c r="I97" s="43"/>
-    </row>
-    <row r="98" spans="1:9">
-      <c r="A98" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="B98" s="43">
-        <v>0.38040000000000002</v>
-      </c>
-      <c r="C98" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D98" s="43"/>
-      <c r="E98" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F98" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="G98" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H98" s="43"/>
-      <c r="I98" s="43"/>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B99" s="43">
-        <v>0.37130000000000002</v>
-      </c>
-      <c r="C99" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D99" s="43"/>
-      <c r="E99" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F99" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="G99" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" s="43"/>
-      <c r="I99" s="43"/>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B100" s="43">
-        <v>9.1000000000000004E-3</v>
-      </c>
-      <c r="C100" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D100" s="43"/>
-      <c r="E100" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F100" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G100" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" s="43"/>
-      <c r="I100" s="43" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9">
-      <c r="A101" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="B101" s="44">
-        <v>5.3483200000000002E-10</v>
-      </c>
-      <c r="C101" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D101" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E101" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F101" s="43"/>
-      <c r="G101" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H101" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="I101" s="43"/>
-    </row>
-    <row r="102" spans="1:9">
-      <c r="A102" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="B102" s="43">
-        <v>5.32728E-4</v>
-      </c>
-      <c r="C102" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D102" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="E102" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="43"/>
-      <c r="G102" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H102" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="I102" s="43"/>
-    </row>
-    <row r="103" spans="1:9">
-      <c r="A103" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="B103" s="43">
-        <v>3.6000000000000001E-5</v>
-      </c>
-      <c r="C103" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D103" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E103" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" s="43"/>
-      <c r="G103" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H103" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="I103" s="43"/>
-    </row>
-    <row r="104" spans="1:9">
-      <c r="A104" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="B104" s="43">
-        <v>3.6240000000000003E-4</v>
-      </c>
-      <c r="C104" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D104" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E104" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="43"/>
-      <c r="G104" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H104" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="I104" s="43"/>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="B105" s="44">
-        <v>2.54628E-9</v>
-      </c>
-      <c r="C105" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D105" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E105" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F105" s="43"/>
-      <c r="G105" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H105" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="I105" s="43"/>
-    </row>
-    <row r="106" spans="1:9">
-      <c r="A106" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="B106" s="43">
-        <v>2.796E-5</v>
-      </c>
-      <c r="C106" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D106" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E106" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="43"/>
-      <c r="G106" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H106" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="I106" s="43"/>
-    </row>
-    <row r="107" spans="1:9">
-      <c r="A107" s="43" t="s">
-        <v>148</v>
-      </c>
-      <c r="B107" s="43">
-        <v>1.668E-5</v>
-      </c>
-      <c r="C107" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D107" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E107" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="43"/>
-      <c r="G107" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H107" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="I107" s="43"/>
-    </row>
-    <row r="108" spans="1:9">
-      <c r="A108" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="B108" s="43">
-        <v>2.0291999999999999E-4</v>
-      </c>
-      <c r="C108" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D108" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E108" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="43"/>
-      <c r="G108" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H108" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="I108" s="43"/>
-    </row>
-    <row r="109" spans="1:9">
-      <c r="A109" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="B109" s="43">
-        <v>3.1236000000000002E-4</v>
-      </c>
-      <c r="C109" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D109" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E109" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F109" s="43"/>
-      <c r="G109" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H109" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="I109" s="43"/>
-    </row>
-    <row r="110" spans="1:9">
-      <c r="A110" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="B110" s="43">
-        <v>4.8000000000000001E-5</v>
-      </c>
-      <c r="C110" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D110" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E110" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F110" s="43"/>
-      <c r="G110" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H110" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="I110" s="43"/>
-    </row>
-    <row r="111" spans="1:9">
-      <c r="A111" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="B111" s="43">
-        <v>1.1592E-5</v>
-      </c>
-      <c r="C111" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D111" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E111" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F111" s="43"/>
-      <c r="G111" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H111" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="I111" s="43"/>
-    </row>
-    <row r="112" spans="1:9">
-      <c r="A112" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B112" s="43">
-        <v>7.538413555</v>
-      </c>
-      <c r="C112" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D112" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="E112" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="43"/>
-      <c r="G112" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H112" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="I112" s="43"/>
-    </row>
-    <row r="113" spans="1:9">
-      <c r="A113" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="B113" s="43">
-        <v>8.8290199999999997E-4</v>
-      </c>
-      <c r="C113" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D113" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E113" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="43"/>
-      <c r="G113" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H113" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="I113" s="43"/>
-    </row>
-    <row r="114" spans="1:9">
-      <c r="A114" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="B114" s="43">
-        <v>3.7139999999999997E-4</v>
-      </c>
-      <c r="C114" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D114" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E114" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="43"/>
-      <c r="G114" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H114" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="I114" s="43"/>
-    </row>
-    <row r="115" spans="1:9">
-      <c r="A115" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="B115" s="43">
-        <v>0</v>
-      </c>
-      <c r="C115" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D115" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="E115" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F115" s="43"/>
-      <c r="G115" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H115" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="I115" s="43"/>
-    </row>
-    <row r="116" spans="1:9">
-      <c r="A116" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="B116" s="43">
-        <v>4.3695687769999996</v>
-      </c>
-      <c r="C116" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D116" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="E116" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F116" s="43"/>
-      <c r="G116" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H116" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="I116" s="43"/>
-    </row>
-    <row r="117" spans="1:9">
-      <c r="A117" s="43"/>
-      <c r="B117" s="43"/>
-      <c r="C117" s="43"/>
-      <c r="D117" s="43"/>
-      <c r="E117" s="43"/>
-      <c r="F117" s="43"/>
-      <c r="G117" s="43"/>
-      <c r="H117" s="43"/>
-      <c r="I117" s="43"/>
-    </row>
-    <row r="118" spans="1:9" ht="15.5">
-      <c r="A118" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B118" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="C118" s="43"/>
-      <c r="D118" s="43"/>
-      <c r="E118" s="43"/>
-      <c r="F118" s="43"/>
-      <c r="G118" s="43"/>
-      <c r="H118" s="43"/>
-      <c r="I118" s="43"/>
-    </row>
-    <row r="119" spans="1:9">
-      <c r="A119" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="B119" s="43">
-        <v>1.290350439</v>
-      </c>
-      <c r="C119" s="43"/>
-      <c r="D119" s="43"/>
-      <c r="E119" s="43"/>
-      <c r="F119" s="43"/>
-      <c r="G119" s="43"/>
-      <c r="H119" s="43"/>
-      <c r="I119" s="43"/>
-    </row>
-    <row r="120" spans="1:9">
-      <c r="A120" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="B120" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="C120" s="43"/>
-      <c r="D120" s="43"/>
-      <c r="E120" s="43"/>
-      <c r="F120" s="43"/>
-      <c r="G120" s="43"/>
-      <c r="H120" s="43"/>
-      <c r="I120" s="43"/>
-    </row>
-    <row r="121" spans="1:9">
-      <c r="A121" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B121" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="C121" s="43"/>
-      <c r="D121" s="43"/>
-      <c r="E121" s="43"/>
-      <c r="F121" s="43"/>
-      <c r="G121" s="43"/>
-      <c r="H121" s="43"/>
-      <c r="I121" s="43"/>
-    </row>
-    <row r="122" spans="1:9">
-      <c r="A122" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B122" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C122" s="43"/>
-      <c r="D122" s="43"/>
-      <c r="E122" s="43"/>
-      <c r="F122" s="43"/>
-      <c r="G122" s="43"/>
-      <c r="H122" s="43"/>
-      <c r="I122" s="43"/>
-    </row>
-    <row r="123" spans="1:9">
-      <c r="A123" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="B123" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C123" s="43"/>
-      <c r="D123" s="43"/>
-      <c r="E123" s="43"/>
-      <c r="F123" s="43"/>
-      <c r="G123" s="43"/>
-      <c r="H123" s="43"/>
-      <c r="I123" s="43"/>
-    </row>
-    <row r="124" spans="1:9" ht="15.5">
-      <c r="A124" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="B124" s="43"/>
-      <c r="C124" s="43"/>
-      <c r="D124" s="43"/>
-      <c r="E124" s="43"/>
-      <c r="F124" s="43"/>
-      <c r="G124" s="43"/>
-      <c r="H124" s="43"/>
-      <c r="I124" s="43"/>
-    </row>
-    <row r="125" spans="1:9">
-      <c r="A125" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B125" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C125" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D125" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="E125" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F125" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G125" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="H125" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I125" s="43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9">
-      <c r="A126" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="B126" s="43">
-        <v>1</v>
-      </c>
-      <c r="C126" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D126" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="E126" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F126" s="43"/>
-      <c r="G126" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="H126" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="I126" s="43"/>
-    </row>
-    <row r="127" spans="1:9">
-      <c r="A127" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="B127" s="44">
-        <v>2.8033E-8</v>
-      </c>
-      <c r="C127" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D127" s="43"/>
-      <c r="E127" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G127" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H127" s="43"/>
-      <c r="I127" s="43"/>
-    </row>
-    <row r="128" spans="1:9">
-      <c r="A128" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="B128" s="44">
-        <v>4.2049500000000003E-6</v>
-      </c>
-      <c r="C128" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D128" s="43"/>
-      <c r="E128" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F128" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G128" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H128" s="43"/>
-      <c r="I128" s="43"/>
-    </row>
-    <row r="129" spans="1:9">
-      <c r="A129" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="B129" s="44">
-        <v>1.12135E-5</v>
-      </c>
-      <c r="C129" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D129" s="43"/>
-      <c r="E129" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G129" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H129" s="43"/>
-      <c r="I129" s="43"/>
-    </row>
-    <row r="130" spans="1:9">
-      <c r="A130" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="B130" s="44">
-        <v>2.8033E-10</v>
-      </c>
-      <c r="C130" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D130" s="43"/>
-      <c r="E130" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F130" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G130" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H130" s="43"/>
-      <c r="I130" s="43"/>
-    </row>
-    <row r="131" spans="1:9">
-      <c r="A131" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="B131" s="44">
-        <v>1.96236E-5</v>
-      </c>
-      <c r="C131" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D131" s="43"/>
-      <c r="E131" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F131" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G131" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H131" s="43"/>
-      <c r="I131" s="43"/>
-    </row>
-    <row r="132" spans="1:9">
-      <c r="A132" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B132" s="43">
-        <v>2.6104586730000001</v>
-      </c>
-      <c r="C132" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D132" s="43"/>
-      <c r="E132" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F132" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G132" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H132" s="43"/>
-      <c r="I132" s="43"/>
-    </row>
-    <row r="133" spans="1:9">
-      <c r="A133" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B133" s="44">
-        <v>5.8870399999999998E-5</v>
-      </c>
-      <c r="C133" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D133" s="43"/>
-      <c r="E133" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G133" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H133" s="43"/>
-      <c r="I133" s="43"/>
-    </row>
-    <row r="134" spans="1:9">
-      <c r="A134" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B134" s="44">
-        <v>2.8032999999999999E-6</v>
-      </c>
-      <c r="C134" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D134" s="43"/>
-      <c r="E134" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G134" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H134" s="43"/>
-      <c r="I134" s="43"/>
-    </row>
-    <row r="135" spans="1:9">
-      <c r="A135" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B135" s="44">
-        <v>2.8032999999999999E-6</v>
-      </c>
-      <c r="C135" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D135" s="43"/>
-      <c r="E135" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F135" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G135" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H135" s="43"/>
-      <c r="I135" s="43"/>
-    </row>
-    <row r="136" spans="1:9">
-      <c r="A136" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B136" s="44">
-        <v>8.4101700000000003E-10</v>
-      </c>
-      <c r="C136" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D136" s="43"/>
-      <c r="E136" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F136" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G136" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H136" s="43"/>
-      <c r="I136" s="43"/>
-    </row>
-    <row r="137" spans="1:9">
-      <c r="A137" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B137" s="44">
-        <v>5.6068700000000001E-5</v>
-      </c>
-      <c r="C137" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D137" s="43"/>
-      <c r="E137" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F137" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G137" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H137" s="43"/>
-      <c r="I137" s="43"/>
-    </row>
-    <row r="138" spans="1:9">
-      <c r="A138" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="B138" s="43">
-        <v>5.0180299999999999E-4</v>
-      </c>
-      <c r="C138" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D138" s="43"/>
-      <c r="E138" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F138" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G138" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H138" s="43"/>
-      <c r="I138" s="43"/>
-    </row>
-    <row r="139" spans="1:9">
-      <c r="A139" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B139" s="44">
-        <v>2.8033000000000002E-7</v>
-      </c>
-      <c r="C139" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D139" s="43"/>
-      <c r="E139" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F139" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G139" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H139" s="43"/>
-      <c r="I139" s="43"/>
-    </row>
-    <row r="140" spans="1:9">
-      <c r="A140" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="B140" s="44">
-        <v>5.6068700000000001E-6</v>
-      </c>
-      <c r="C140" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D140" s="43"/>
-      <c r="E140" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F140" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G140" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H140" s="43"/>
-      <c r="I140" s="43"/>
-    </row>
-    <row r="141" spans="1:9">
-      <c r="A141" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B141" s="44">
-        <v>3.36417E-5</v>
-      </c>
-      <c r="C141" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D141" s="43"/>
-      <c r="E141" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F141" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G141" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H141" s="43"/>
-      <c r="I141" s="43"/>
-    </row>
-    <row r="142" spans="1:9">
-      <c r="A142" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B142" s="44">
-        <v>5.6068700000000001E-6</v>
-      </c>
-      <c r="C142" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D142" s="43"/>
-      <c r="E142" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F142" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G142" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H142" s="43"/>
-      <c r="I142" s="43"/>
-    </row>
-    <row r="143" spans="1:9">
-      <c r="A143" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B143" s="44">
-        <v>5.6068700000000005E-7</v>
-      </c>
-      <c r="C143" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D143" s="43"/>
-      <c r="E143" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F143" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G143" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H143" s="43"/>
-      <c r="I143" s="43"/>
-    </row>
-    <row r="144" spans="1:9">
-      <c r="A144" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="B144" s="44">
-        <v>1.5418699999999999E-5</v>
-      </c>
-      <c r="C144" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D144" s="43"/>
-      <c r="E144" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F144" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G144" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H144" s="43"/>
-      <c r="I144" s="43"/>
-    </row>
-    <row r="145" spans="1:9">
-      <c r="A145" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B145" s="44">
-        <v>5.6068700000000001E-6</v>
-      </c>
-      <c r="C145" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D145" s="43"/>
-      <c r="E145" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F145" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G145" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H145" s="43"/>
-      <c r="I145" s="43"/>
-    </row>
-    <row r="146" spans="1:9">
-      <c r="A146" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="B146" s="43">
-        <v>0.38033800800000001</v>
-      </c>
-      <c r="C146" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D146" s="43"/>
-      <c r="E146" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F146" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="G146" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H146" s="43"/>
-      <c r="I146" s="43"/>
-    </row>
-    <row r="147" spans="1:9">
-      <c r="A147" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B147" s="43">
-        <v>0.36940000000000001</v>
-      </c>
-      <c r="C147" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D147" s="43"/>
-      <c r="E147" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F147" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="G147" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H147" s="43"/>
-      <c r="I147" s="43"/>
-    </row>
-    <row r="148" spans="1:9">
-      <c r="A148" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B148" s="43">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="C148" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D148" s="43"/>
-      <c r="E148" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F148" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G148" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H148" s="43"/>
-      <c r="I148" s="43" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9">
-      <c r="A149" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="B149" s="43">
-        <v>6.1611670199999997</v>
-      </c>
-      <c r="C149" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D149" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E149" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F149" s="43"/>
-      <c r="G149" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H149" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="I149" s="43"/>
-    </row>
-    <row r="150" spans="1:9">
-      <c r="A150" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="B150" s="44">
-        <v>5.3477100000000001E-10</v>
-      </c>
-      <c r="C150" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D150" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E150" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F150" s="43"/>
-      <c r="G150" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H150" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="I150" s="43"/>
-    </row>
-    <row r="151" spans="1:9">
-      <c r="A151" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="B151" s="43">
-        <v>5.32728E-4</v>
-      </c>
-      <c r="C151" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D151" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="E151" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" s="43"/>
-      <c r="G151" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H151" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="I151" s="43"/>
-    </row>
-    <row r="152" spans="1:9">
-      <c r="A152" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="B152" s="43">
-        <v>3.6000000000000001E-5</v>
-      </c>
-      <c r="C152" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D152" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E152" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F152" s="43"/>
-      <c r="G152" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H152" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="I152" s="43"/>
-    </row>
-    <row r="153" spans="1:9">
-      <c r="A153" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="B153" s="43">
-        <v>3.6240000000000003E-4</v>
-      </c>
-      <c r="C153" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D153" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E153" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F153" s="43"/>
-      <c r="G153" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H153" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="I153" s="43"/>
-    </row>
-    <row r="154" spans="1:9">
-      <c r="A154" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="B154" s="43">
-        <v>2.0948000000000001E-4</v>
-      </c>
-      <c r="C154" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D154" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E154" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F154" s="43"/>
-      <c r="G154" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H154" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="I154" s="43"/>
-    </row>
-    <row r="155" spans="1:9">
-      <c r="A155" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="B155" s="44">
-        <v>2.54628E-9</v>
-      </c>
-      <c r="C155" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D155" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E155" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F155" s="43"/>
-      <c r="G155" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H155" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="I155" s="43"/>
-    </row>
-    <row r="156" spans="1:9">
-      <c r="A156" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="B156" s="43">
-        <v>2.796E-5</v>
-      </c>
-      <c r="C156" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D156" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E156" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F156" s="43"/>
-      <c r="G156" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H156" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="I156" s="43"/>
-    </row>
-    <row r="157" spans="1:9">
-      <c r="A157" s="43" t="s">
-        <v>148</v>
-      </c>
-      <c r="B157" s="43">
-        <v>1.668E-5</v>
-      </c>
-      <c r="C157" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D157" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E157" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F157" s="43"/>
-      <c r="G157" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H157" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="I157" s="43"/>
-    </row>
-    <row r="158" spans="1:9">
-      <c r="A158" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="B158" s="43">
-        <v>2.0291999999999999E-4</v>
-      </c>
-      <c r="C158" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D158" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E158" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F158" s="43"/>
-      <c r="G158" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H158" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="I158" s="43"/>
-    </row>
-    <row r="159" spans="1:9">
-      <c r="A159" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="B159" s="43">
-        <v>3.1236000000000002E-4</v>
-      </c>
-      <c r="C159" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D159" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E159" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" s="43"/>
-      <c r="G159" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H159" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="I159" s="43"/>
-    </row>
-    <row r="160" spans="1:9">
-      <c r="A160" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="B160" s="43">
-        <v>4.8000000000000001E-5</v>
-      </c>
-      <c r="C160" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D160" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E160" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F160" s="43"/>
-      <c r="G160" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H160" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="I160" s="43"/>
-    </row>
-    <row r="161" spans="1:9">
-      <c r="A161" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="B161" s="43">
-        <v>1.1592E-5</v>
-      </c>
-      <c r="C161" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D161" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E161" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F161" s="43"/>
-      <c r="G161" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H161" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="I161" s="43"/>
-    </row>
-    <row r="162" spans="1:9">
-      <c r="A162" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B162" s="43">
-        <v>7.5375498600000004</v>
-      </c>
-      <c r="C162" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D162" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="E162" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F162" s="43"/>
-      <c r="G162" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H162" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="I162" s="43"/>
-    </row>
-    <row r="163" spans="1:9">
-      <c r="A163" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="B163" s="43">
-        <v>8.8290199999999997E-4</v>
-      </c>
-      <c r="C163" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D163" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E163" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="43"/>
-      <c r="G163" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H163" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="I163" s="43"/>
-    </row>
-    <row r="164" spans="1:9">
-      <c r="A164" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="B164" s="43">
-        <v>3.7139999999999997E-4</v>
-      </c>
-      <c r="C164" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D164" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E164" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F164" s="43"/>
-      <c r="G164" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H164" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="I164" s="43"/>
-    </row>
-    <row r="165" spans="1:9">
-      <c r="A165" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="B165" s="43">
-        <v>0</v>
-      </c>
-      <c r="C165" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D165" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="E165" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F165" s="43"/>
-      <c r="G165" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H165" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="I165" s="43"/>
-    </row>
-    <row r="166" spans="1:9">
-      <c r="A166" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="B166" s="43">
-        <v>4.3011681309999998</v>
-      </c>
-      <c r="C166" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D166" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="E166" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F166" s="43"/>
-      <c r="G166" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H166" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="I166" s="43"/>
-    </row>
-    <row r="168" spans="1:9" ht="15.5">
-      <c r="A168" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B168" s="34" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9">
-      <c r="A169" t="s">
-        <v>2</v>
-      </c>
-      <c r="B169" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9">
-      <c r="A170" t="s">
-        <v>11</v>
-      </c>
-      <c r="B170" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9">
-      <c r="A171" t="s">
-        <v>3</v>
-      </c>
-      <c r="B171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9">
-      <c r="A172" t="s">
-        <v>76</v>
-      </c>
-      <c r="B172"/>
-    </row>
-    <row r="173" spans="1:9">
-      <c r="A173" t="s">
-        <v>4</v>
-      </c>
-      <c r="B173" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9">
-      <c r="A174" t="s">
-        <v>5</v>
-      </c>
-      <c r="B174" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9">
-      <c r="A175" t="s">
-        <v>6</v>
-      </c>
-      <c r="B175" s="43" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" ht="15.5">
-      <c r="A176" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B176"/>
-    </row>
-    <row r="177" spans="1:8" ht="15.5">
-      <c r="A177" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B177" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C177" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D177" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="E177" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F177" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="G177" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="H177" s="34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
-      <c r="A178" t="str">
-        <f>B168</f>
-        <v>empty activity, for market that does not exist any more in 2050, Tr2050</v>
-      </c>
-      <c r="B178">
-        <v>1</v>
-      </c>
-      <c r="C178" t="s">
-        <v>29</v>
-      </c>
-      <c r="D178" t="str">
-        <f>B175</f>
-        <v>kilogram</v>
-      </c>
-      <c r="F178" t="s">
-        <v>18</v>
-      </c>
-      <c r="G178" t="str">
-        <f>B173</f>
+      <c r="G81" t="str">
+        <f>B76</f>
         <v>nothing</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
-      <c r="B179"/>
-    </row>
-    <row r="180" spans="1:8">
-      <c r="B180" s="41"/>
-    </row>
-    <row r="181" spans="1:8">
-      <c r="B181" s="41"/>
-    </row>
-    <row r="182" spans="1:8">
-      <c r="B182" s="41"/>
-    </row>
-    <row r="183" spans="1:8">
-      <c r="B183"/>
-    </row>
-    <row r="184" spans="1:8">
-      <c r="B184"/>
-    </row>
-    <row r="185" spans="1:8">
-      <c r="B185"/>
+    <row r="82" spans="1:7">
+      <c r="B82"/>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="B83" s="41"/>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="B84" s="41"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="B85" s="41"/>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="B86"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="B87"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="B88"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4738,7 +2354,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -4746,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
@@ -5010,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>

--- a/inventories/lci-Tr2050.xlsx
+++ b/inventories/lci-Tr2050.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie-my.sharepoint.com/personal/db6421_engie_com/Documents/Documents/GitHub/ADEME_scenarios_premise_gas/inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1718" documentId="13_ncr:1_{6A9A1C53-53B4-4DAF-B82F-70FF83AECA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FDF5E9E-0A4E-4357-85CA-802D21303263}"/>
+  <xr:revisionPtr revIDLastSave="1759" documentId="13_ncr:1_{6A9A1C53-53B4-4DAF-B82F-70FF83AECA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D0D3474-BBD2-4870-A7ED-E2183A0A0CA7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lci" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3936" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3934" uniqueCount="480">
   <si>
     <t>Database</t>
   </si>
@@ -815,9 +815,6 @@
     <t>biomethane AD transport</t>
   </si>
   <si>
-    <t>market for heat, central or small-scale, biomethane</t>
-  </si>
-  <si>
     <t>heat, central or small-scale, biomethane</t>
   </si>
   <si>
@@ -950,21 +947,12 @@
     <t>Import of biomethane (anaerobic digestion and gasification of wood)</t>
   </si>
   <si>
-    <t>5.93e-03 MJ heat/MJ natural gas high pressure (Faist Emmenegger et al., 2017). Biomethane LHV = 34.72 MJ considering a constant upgrading mix</t>
-  </si>
-  <si>
     <t>Scaled to reference product based on ecoinvent Faist Emmenegger M., Del Duce A., Moreno Ruiz E., Brunner F., (2017). Update of the European natural gas supply chains. Ecoinvent, Zürich, Switzerland</t>
   </si>
   <si>
     <t>market for biogas</t>
   </si>
   <si>
-    <t>5.93e-03 MJ heat/MJ natural gas high pressure (Faist Emmenegger et al., 2017).LHV = 35</t>
-  </si>
-  <si>
-    <t>1.5% of losses (ADEME Transition 2050)</t>
-  </si>
-  <si>
     <t>1.5% ADEME Transition 2050. Calculated from the estimated composition of biomethane from AD in the French mix after upgrading</t>
   </si>
   <si>
@@ -1482,6 +1470,12 @@
   </si>
   <si>
     <t>platinum group metal, extraction and refinery operations</t>
+  </si>
+  <si>
+    <t>1.5% of losses including the burned natural gas (ADEME Transition 2050)</t>
+  </si>
+  <si>
+    <t>heat production, biomethane, at boiler condensing modulating &lt;100kW</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1632,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1720,6 +1714,7 @@
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1739,10 +1734,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2009,17 +2000,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH923"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="73.109375" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="109.6640625" customWidth="1"/>
+    <col min="1" max="1" width="73.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="109.7109375" customWidth="1"/>
     <col min="10" max="10" width="31" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2071,7 +2062,7 @@
       <c r="I4" s="6"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:14" ht="15.6">
+    <row r="5" spans="1:14" ht="15.75">
       <c r="A5" s="18" t="s">
         <v>1</v>
       </c>
@@ -2153,7 +2144,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15.6">
+    <row r="13" spans="1:14" ht="15.75">
       <c r="A13" s="18" t="s">
         <v>7</v>
       </c>
@@ -2162,7 +2153,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15.6">
+    <row r="14" spans="1:14" ht="15.75">
       <c r="A14" s="18" t="s">
         <v>8</v>
       </c>
@@ -2875,7 +2866,7 @@
       <c r="AG47" s="47"/>
       <c r="AH47" s="47"/>
     </row>
-    <row r="48" spans="1:34" s="15" customFormat="1" ht="15.6">
+    <row r="48" spans="1:34" s="15" customFormat="1" ht="15.75">
       <c r="A48" s="2" t="s">
         <v>1</v>
       </c>
@@ -2895,7 +2886,7 @@
       <c r="O48" s="16"/>
       <c r="P48" s="16"/>
     </row>
-    <row r="49" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="49" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A49" s="2" t="s">
         <v>3</v>
       </c>
@@ -2915,7 +2906,7 @@
       <c r="O49" s="16"/>
       <c r="P49" s="16"/>
     </row>
-    <row r="50" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="50" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -2935,7 +2926,7 @@
       <c r="O50" s="16"/>
       <c r="P50" s="16"/>
     </row>
-    <row r="51" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="51" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A51" s="2" t="s">
         <v>4</v>
       </c>
@@ -2955,7 +2946,7 @@
       <c r="O51" s="16"/>
       <c r="P51" s="16"/>
     </row>
-    <row r="52" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="52" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A52" s="2" t="s">
         <v>2</v>
       </c>
@@ -2975,7 +2966,7 @@
       <c r="O52" s="16"/>
       <c r="P52" s="16"/>
     </row>
-    <row r="53" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="53" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
@@ -2997,7 +2988,7 @@
       <c r="O53" s="16"/>
       <c r="P53" s="16"/>
     </row>
-    <row r="54" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="54" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -3017,7 +3008,7 @@
       <c r="O54" s="16"/>
       <c r="P54" s="16"/>
     </row>
-    <row r="55" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="55" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A55" s="2" t="s">
         <v>8</v>
       </c>
@@ -3055,7 +3046,7 @@
       <c r="S55" s="17"/>
       <c r="T55" s="18"/>
     </row>
-    <row r="56" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="56" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -3087,7 +3078,7 @@
       <c r="P56" s="16"/>
       <c r="T56"/>
     </row>
-    <row r="57" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="57" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -3121,7 +3112,7 @@
       <c r="Q57"/>
       <c r="R57"/>
     </row>
-    <row r="58" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="58" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A58" t="s">
         <v>53</v>
       </c>
@@ -3155,7 +3146,7 @@
       <c r="Q58"/>
       <c r="R58"/>
     </row>
-    <row r="59" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="59" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A59" t="s">
         <v>43</v>
       </c>
@@ -3189,7 +3180,7 @@
       <c r="Q59"/>
       <c r="R59"/>
     </row>
-    <row r="60" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="60" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A60" t="s">
         <v>46</v>
       </c>
@@ -3223,7 +3214,7 @@
       <c r="Q60"/>
       <c r="R60"/>
     </row>
-    <row r="61" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="61" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -3256,7 +3247,7 @@
       <c r="Q61"/>
       <c r="R61"/>
     </row>
-    <row r="62" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="62" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -3289,7 +3280,7 @@
       <c r="Q62"/>
       <c r="R62"/>
     </row>
-    <row r="63" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="63" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -3318,7 +3309,7 @@
       <c r="Q63" s="20"/>
       <c r="R63"/>
     </row>
-    <row r="64" spans="1:20" s="15" customFormat="1" ht="15.6">
+    <row r="64" spans="1:20" s="15" customFormat="1" ht="15.75">
       <c r="A64" t="s">
         <v>51</v>
       </c>
@@ -3387,7 +3378,7 @@
       <c r="AG65" s="47"/>
       <c r="AH65" s="47"/>
     </row>
-    <row r="66" spans="1:34" ht="15.6">
+    <row r="66" spans="1:34" ht="15.75">
       <c r="A66" s="18" t="s">
         <v>1</v>
       </c>
@@ -3449,13 +3440,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:34" ht="15.6">
+    <row r="74" spans="1:34" ht="15.75">
       <c r="A74" s="18" t="s">
         <v>7</v>
       </c>
       <c r="B74"/>
     </row>
-    <row r="75" spans="1:34" ht="15.6">
+    <row r="75" spans="1:34" ht="15.75">
       <c r="A75" s="18" t="s">
         <v>8</v>
       </c>
@@ -3585,7 +3576,7 @@
         <v>11</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="26"/>
@@ -4691,7 +4682,7 @@
         <v>11</v>
       </c>
       <c r="B103" s="26" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C103" s="25"/>
       <c r="D103" s="26"/>
@@ -5747,7 +5738,7 @@
         <v>11</v>
       </c>
       <c r="B126" s="26" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C126" s="25"/>
       <c r="D126" s="26"/>
@@ -6803,7 +6794,7 @@
         <v>11</v>
       </c>
       <c r="B149" s="26" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C149" s="25"/>
       <c r="D149" s="26"/>
@@ -7887,7 +7878,7 @@
         <v>11</v>
       </c>
       <c r="B173" s="26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C173" s="25"/>
       <c r="D173" s="26"/>
@@ -8756,7 +8747,7 @@
         <v>11</v>
       </c>
       <c r="B197" s="26" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C197" s="25"/>
       <c r="D197" s="26"/>
@@ -9133,10 +9124,10 @@
     </row>
     <row r="206" spans="1:34">
       <c r="A206" s="26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B206" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C206" s="32">
         <v>5.2260830394610069</v>
@@ -9791,7 +9782,7 @@
         <v>11</v>
       </c>
       <c r="B221" s="26" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C221" s="25"/>
       <c r="D221" s="26"/>
@@ -10605,7 +10596,7 @@
         <v>11</v>
       </c>
       <c r="B245" s="26" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C245" s="25"/>
       <c r="D245" s="26"/>
@@ -11384,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="B268" s="24" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C268" s="22"/>
       <c r="D268" s="22"/>
@@ -11444,7 +11435,7 @@
         <v>4</v>
       </c>
       <c r="B271" s="22" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C271" s="22"/>
       <c r="D271" s="22"/>
@@ -11464,7 +11455,7 @@
         <v>57</v>
       </c>
       <c r="B272" s="31" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C272" s="22"/>
       <c r="D272" s="22"/>
@@ -11548,10 +11539,10 @@
     </row>
     <row r="276" spans="1:14">
       <c r="A276" s="22" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B276" s="22" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C276" s="22">
         <v>1</v>
@@ -11574,10 +11565,10 @@
     </row>
     <row r="277" spans="1:14">
       <c r="A277" s="22" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B277" s="22" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C277" s="22">
         <v>8.9499999999999996E-3</v>
@@ -11596,7 +11587,7 @@
         <v>12</v>
       </c>
       <c r="I277" s="22" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K277" s="22"/>
       <c r="L277" s="22"/>
@@ -11605,7 +11596,7 @@
     </row>
     <row r="278" spans="1:14">
       <c r="A278" s="22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B278" s="22" t="s">
         <v>99</v>
@@ -11627,7 +11618,7 @@
         <v>12</v>
       </c>
       <c r="I278" s="22" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="K278" s="22"/>
       <c r="L278" s="22"/>
@@ -11658,7 +11649,7 @@
         <v>12</v>
       </c>
       <c r="I279" s="22" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="K279" s="22"/>
       <c r="L279" s="22"/>
@@ -11667,10 +11658,10 @@
     </row>
     <row r="280" spans="1:14">
       <c r="A280" s="22" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B280" s="22" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C280" s="22">
         <v>1.79E-6</v>
@@ -11689,7 +11680,7 @@
         <v>12</v>
       </c>
       <c r="I280" s="22" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="K280" s="22"/>
       <c r="L280" s="22"/>
@@ -11698,10 +11689,10 @@
     </row>
     <row r="281" spans="1:14">
       <c r="A281" s="22" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B281" s="22" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C281" s="22">
         <v>9.859999999999999E-4</v>
@@ -11720,7 +11711,7 @@
         <v>12</v>
       </c>
       <c r="I281" s="22" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="K281" s="22"/>
       <c r="L281" s="22"/>
@@ -11729,10 +11720,10 @@
     </row>
     <row r="282" spans="1:14">
       <c r="A282" s="22" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B282" s="22" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C282" s="22">
         <v>5.3699999999999998E-3</v>
@@ -11751,7 +11742,7 @@
         <v>12</v>
       </c>
       <c r="I282" s="22" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="K282" s="22"/>
       <c r="L282" s="22"/>
@@ -11760,10 +11751,10 @@
     </row>
     <row r="283" spans="1:14">
       <c r="A283" s="22" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B283" s="22" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C283" s="22">
         <v>5.3699999999999998E-3</v>
@@ -11782,7 +11773,7 @@
         <v>12</v>
       </c>
       <c r="I283" s="22" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K283" s="22"/>
       <c r="L283" s="22"/>
@@ -11791,10 +11782,10 @@
     </row>
     <row r="284" spans="1:14">
       <c r="A284" s="22" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B284" s="22" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C284" s="22">
         <v>2.3300000000000001E-2</v>
@@ -11813,7 +11804,7 @@
         <v>12</v>
       </c>
       <c r="I284" s="22" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="K284" s="22"/>
       <c r="L284" s="22"/>
@@ -11822,10 +11813,10 @@
     </row>
     <row r="285" spans="1:14">
       <c r="A285" s="22" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B285" s="22" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C285" s="22">
         <v>0.55700000000000005</v>
@@ -11844,7 +11835,7 @@
         <v>12</v>
       </c>
       <c r="I285" s="22" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="K285" s="22"/>
       <c r="L285" s="22"/>
@@ -11875,7 +11866,7 @@
         <v>12</v>
       </c>
       <c r="I286" s="22" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="K286" s="22"/>
       <c r="L286" s="22"/>
@@ -11906,7 +11897,7 @@
         <v>12</v>
       </c>
       <c r="I287" s="22" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="K287" s="22"/>
       <c r="L287" s="22"/>
@@ -11915,10 +11906,10 @@
     </row>
     <row r="288" spans="1:14">
       <c r="A288" s="22" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B288" s="22" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C288" s="22">
         <v>3.9199999999999999E-3</v>
@@ -11937,7 +11928,7 @@
         <v>12</v>
       </c>
       <c r="I288" s="22" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="K288" s="22"/>
       <c r="L288" s="22"/>
@@ -11966,7 +11957,7 @@
         <v>15</v>
       </c>
       <c r="I289" s="22" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K289" s="22"/>
       <c r="L289" s="22"/>
@@ -11995,7 +11986,7 @@
         <v>15</v>
       </c>
       <c r="I290" s="22" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K290" s="22"/>
       <c r="L290" s="22"/>
@@ -12004,7 +11995,7 @@
     </row>
     <row r="291" spans="1:14">
       <c r="A291" s="22" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C291" s="22">
         <v>15.4</v>
@@ -12017,13 +12008,13 @@
       </c>
       <c r="F291" s="22"/>
       <c r="G291" s="22" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H291" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I291" s="22" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J291" s="22"/>
       <c r="K291" s="22"/>
@@ -12052,7 +12043,7 @@
         <v>15</v>
       </c>
       <c r="I292" s="22" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="J292" s="22"/>
       <c r="K292" s="22"/>
@@ -12062,7 +12053,7 @@
     </row>
     <row r="293" spans="1:14">
       <c r="A293" s="22" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C293" s="22">
         <v>1.4</v>
@@ -12081,7 +12072,7 @@
         <v>15</v>
       </c>
       <c r="I293" s="22" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J293" s="22"/>
       <c r="K293" s="22"/>
@@ -12091,7 +12082,7 @@
     </row>
     <row r="294" spans="1:14">
       <c r="A294" s="22" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C294" s="22">
         <v>1.4</v>
@@ -12110,7 +12101,7 @@
         <v>15</v>
       </c>
       <c r="I294" s="22" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J294" s="22"/>
       <c r="K294" s="22"/>
@@ -12120,7 +12111,7 @@
     </row>
     <row r="295" spans="1:14">
       <c r="A295" s="22" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C295" s="22">
         <v>1.4</v>
@@ -12139,7 +12130,7 @@
         <v>15</v>
       </c>
       <c r="I295" s="22" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J295" s="22"/>
       <c r="K295" s="22"/>
@@ -12168,7 +12159,7 @@
         <v>15</v>
       </c>
       <c r="I296" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J296" s="22"/>
       <c r="K296" s="22"/>
@@ -12197,7 +12188,7 @@
         <v>15</v>
       </c>
       <c r="I297" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J297" s="22"/>
       <c r="K297" s="22"/>
@@ -12226,7 +12217,7 @@
         <v>15</v>
       </c>
       <c r="I298" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J298" s="22"/>
       <c r="K298" s="22"/>
@@ -12236,7 +12227,7 @@
     </row>
     <row r="299" spans="1:14">
       <c r="A299" s="22" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C299" s="22">
         <v>0.48</v>
@@ -12255,7 +12246,7 @@
         <v>15</v>
       </c>
       <c r="I299" s="22" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J299" s="22"/>
       <c r="K299" s="22"/>
@@ -12265,7 +12256,7 @@
     </row>
     <row r="300" spans="1:14">
       <c r="A300" s="22" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C300" s="22">
         <v>0.48</v>
@@ -12284,7 +12275,7 @@
         <v>15</v>
       </c>
       <c r="I300" s="22" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J300" s="22"/>
       <c r="K300" s="22"/>
@@ -12294,7 +12285,7 @@
     </row>
     <row r="301" spans="1:14">
       <c r="A301" s="22" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C301" s="22">
         <v>0.96</v>
@@ -12313,7 +12304,7 @@
         <v>15</v>
       </c>
       <c r="I301" s="22" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="J301" s="22"/>
       <c r="K301" s="22"/>
@@ -12323,7 +12314,7 @@
     </row>
     <row r="302" spans="1:14">
       <c r="A302" s="22" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C302" s="22">
         <v>1.0100000000000001E-6</v>
@@ -12336,13 +12327,13 @@
       </c>
       <c r="F302" s="22"/>
       <c r="G302" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H302" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J302" s="22"/>
       <c r="K302" s="22"/>
@@ -12352,7 +12343,7 @@
     </row>
     <row r="303" spans="1:14">
       <c r="A303" s="22" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C303" s="22">
         <v>6.1399999999999997E-7</v>
@@ -12365,13 +12356,13 @@
       </c>
       <c r="F303" s="22"/>
       <c r="G303" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H303" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I303" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J303" s="22"/>
       <c r="K303" s="22"/>
@@ -12381,7 +12372,7 @@
     </row>
     <row r="304" spans="1:14">
       <c r="A304" s="22" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C304" s="22">
         <v>4.8099999999999997E-9</v>
@@ -12394,13 +12385,13 @@
       </c>
       <c r="F304" s="22"/>
       <c r="G304" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H304" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I304" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J304" s="22"/>
       <c r="K304" s="22"/>
@@ -12410,7 +12401,7 @@
     </row>
     <row r="305" spans="1:14">
       <c r="A305" s="22" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C305" s="22">
         <v>6.5000000000000002E-7</v>
@@ -12423,13 +12414,13 @@
       </c>
       <c r="F305" s="22"/>
       <c r="G305" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H305" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I305" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J305" s="22"/>
       <c r="K305" s="22"/>
@@ -12439,7 +12430,7 @@
     </row>
     <row r="306" spans="1:14">
       <c r="A306" s="22" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C306" s="22">
         <v>-1.5E-6</v>
@@ -12452,13 +12443,13 @@
       </c>
       <c r="F306" s="22"/>
       <c r="G306" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H306" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I306" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J306" s="22"/>
       <c r="K306" s="22"/>
@@ -12468,7 +12459,7 @@
     </row>
     <row r="307" spans="1:14">
       <c r="A307" s="22" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C307" s="22">
         <v>1.1999999999999999E-7</v>
@@ -12481,13 +12472,13 @@
       </c>
       <c r="F307" s="22"/>
       <c r="G307" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H307" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I307" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J307" s="22"/>
       <c r="K307" s="22"/>
@@ -12497,7 +12488,7 @@
     </row>
     <row r="308" spans="1:14">
       <c r="A308" s="22" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C308" s="22">
         <v>2.48E-6</v>
@@ -12510,13 +12501,13 @@
       </c>
       <c r="F308" s="22"/>
       <c r="G308" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H308" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I308" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J308" s="22"/>
       <c r="K308" s="22"/>
@@ -12526,7 +12517,7 @@
     </row>
     <row r="309" spans="1:14">
       <c r="A309" s="22" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C309" s="22">
         <v>1.08E-7</v>
@@ -12539,13 +12530,13 @@
       </c>
       <c r="F309" s="22"/>
       <c r="G309" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H309" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I309" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J309" s="22"/>
       <c r="K309" s="22"/>
@@ -12555,7 +12546,7 @@
     </row>
     <row r="310" spans="1:14">
       <c r="A310" s="22" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C310" s="22">
         <v>1.0100000000000001E-6</v>
@@ -12568,13 +12559,13 @@
       </c>
       <c r="F310" s="22"/>
       <c r="G310" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H310" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I310" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J310" s="22"/>
       <c r="K310" s="22"/>
@@ -12584,7 +12575,7 @@
     </row>
     <row r="311" spans="1:14">
       <c r="A311" s="22" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C311" s="22">
         <v>2.4100000000000001E-8</v>
@@ -12597,13 +12588,13 @@
       </c>
       <c r="F311" s="22"/>
       <c r="G311" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H311" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I311" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J311" s="22"/>
       <c r="K311" s="22"/>
@@ -12613,7 +12604,7 @@
     </row>
     <row r="312" spans="1:14">
       <c r="A312" s="22" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C312" s="22">
         <v>-3.2899999999999999E-7</v>
@@ -12626,13 +12617,13 @@
       </c>
       <c r="F312" s="22"/>
       <c r="G312" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H312" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I312" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J312" s="22"/>
       <c r="K312" s="22"/>
@@ -12642,7 +12633,7 @@
     </row>
     <row r="313" spans="1:14">
       <c r="A313" s="22" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C313" s="22">
         <v>7.9400000000000004E-7</v>
@@ -12655,13 +12646,13 @@
       </c>
       <c r="F313" s="22"/>
       <c r="G313" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H313" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I313" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J313" s="22"/>
       <c r="K313" s="22"/>
@@ -12671,7 +12662,7 @@
     </row>
     <row r="314" spans="1:14">
       <c r="A314" s="22" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C314" s="22">
         <v>4.1400000000000002E-6</v>
@@ -12684,13 +12675,13 @@
       </c>
       <c r="F314" s="22"/>
       <c r="G314" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H314" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I314" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J314" s="22"/>
       <c r="K314" s="22"/>
@@ -12700,7 +12691,7 @@
     </row>
     <row r="315" spans="1:14">
       <c r="A315" s="22" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C315" s="22">
         <v>5.0500000000000002E-8</v>
@@ -12713,13 +12704,13 @@
       </c>
       <c r="F315" s="22"/>
       <c r="G315" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H315" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I315" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J315" s="22"/>
       <c r="K315" s="22"/>
@@ -12729,7 +12720,7 @@
     </row>
     <row r="316" spans="1:14">
       <c r="A316" s="22" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C316" s="22">
         <v>-5.9000000000000003E-6</v>
@@ -12742,13 +12733,13 @@
       </c>
       <c r="F316" s="22"/>
       <c r="G316" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H316" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I316" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J316" s="22"/>
       <c r="K316" s="22"/>
@@ -12758,7 +12749,7 @@
     </row>
     <row r="317" spans="1:14">
       <c r="A317" s="22" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C317" s="22">
         <v>1.5600000000000001E-6</v>
@@ -12771,13 +12762,13 @@
       </c>
       <c r="F317" s="22"/>
       <c r="G317" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H317" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I317" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J317" s="22"/>
       <c r="K317" s="22"/>
@@ -12787,7 +12778,7 @@
     </row>
     <row r="318" spans="1:14">
       <c r="A318" s="22" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C318" s="22">
         <v>2.7E-6</v>
@@ -12800,13 +12791,13 @@
       </c>
       <c r="F318" s="22"/>
       <c r="G318" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H318" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I318" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J318" s="22"/>
       <c r="K318" s="22"/>
@@ -12816,7 +12807,7 @@
     </row>
     <row r="319" spans="1:14">
       <c r="A319" s="22" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C319" s="22">
         <v>4.4500000000000001E-8</v>
@@ -12829,13 +12820,13 @@
       </c>
       <c r="F319" s="22"/>
       <c r="G319" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H319" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I319" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J319" s="22"/>
       <c r="K319" s="22"/>
@@ -12845,7 +12836,7 @@
     </row>
     <row r="320" spans="1:14">
       <c r="A320" s="22" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C320" s="22">
         <v>3.6099999999999999E-8</v>
@@ -12858,13 +12849,13 @@
       </c>
       <c r="F320" s="22"/>
       <c r="G320" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H320" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I320" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J320" s="22"/>
       <c r="K320" s="22"/>
@@ -12874,7 +12865,7 @@
     </row>
     <row r="321" spans="1:14">
       <c r="A321" s="22" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C321" s="22">
         <v>2.17E-7</v>
@@ -12887,13 +12878,13 @@
       </c>
       <c r="F321" s="22"/>
       <c r="G321" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H321" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I321" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J321" s="22"/>
       <c r="K321" s="22"/>
@@ -12903,7 +12894,7 @@
     </row>
     <row r="322" spans="1:14">
       <c r="A322" s="22" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C322" s="22">
         <v>-1.88E-8</v>
@@ -12916,13 +12907,13 @@
       </c>
       <c r="F322" s="22"/>
       <c r="G322" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H322" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I322" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J322" s="22"/>
       <c r="K322" s="22"/>
@@ -12932,7 +12923,7 @@
     </row>
     <row r="323" spans="1:14">
       <c r="A323" s="22" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C323" s="22">
         <v>4.2899999999999999E-5</v>
@@ -12945,13 +12936,13 @@
       </c>
       <c r="F323" s="22"/>
       <c r="G323" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H323" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I323" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J323" s="22"/>
       <c r="K323" s="22"/>
@@ -12961,7 +12952,7 @@
     </row>
     <row r="324" spans="1:14">
       <c r="A324" s="22" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C324" s="22">
         <v>9.2499999999999999E-5</v>
@@ -12974,13 +12965,13 @@
       </c>
       <c r="F324" s="22"/>
       <c r="G324" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H324" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I324" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J324" s="22"/>
       <c r="K324" s="22"/>
@@ -12990,7 +12981,7 @@
     </row>
     <row r="325" spans="1:14">
       <c r="A325" s="22" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C325" s="22">
         <v>5.0300000000000001E-6</v>
@@ -13003,13 +12994,13 @@
       </c>
       <c r="F325" s="22"/>
       <c r="G325" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H325" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I325" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J325" s="22"/>
       <c r="K325" s="22"/>
@@ -13019,7 +13010,7 @@
     </row>
     <row r="326" spans="1:14">
       <c r="A326" s="22" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C326" s="22">
         <v>2.43E-6</v>
@@ -13032,13 +13023,13 @@
       </c>
       <c r="F326" s="22"/>
       <c r="G326" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H326" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I326" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J326" s="22"/>
       <c r="K326" s="22"/>
@@ -13048,7 +13039,7 @@
     </row>
     <row r="327" spans="1:14">
       <c r="A327" s="22" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C327" s="22">
         <v>1.73E-6</v>
@@ -13061,13 +13052,13 @@
       </c>
       <c r="F327" s="22"/>
       <c r="G327" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H327" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I327" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J327" s="22"/>
       <c r="K327" s="22"/>
@@ -13077,7 +13068,7 @@
     </row>
     <row r="328" spans="1:14">
       <c r="A328" s="22" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C328" s="22">
         <v>2.8900000000000001E-7</v>
@@ -13090,13 +13081,13 @@
       </c>
       <c r="F328" s="22"/>
       <c r="G328" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H328" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I328" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J328" s="22"/>
       <c r="K328" s="22"/>
@@ -13106,7 +13097,7 @@
     </row>
     <row r="329" spans="1:14">
       <c r="A329" s="22" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C329" s="22">
         <v>1.9700000000000001E-5</v>
@@ -13119,13 +13110,13 @@
       </c>
       <c r="F329" s="22"/>
       <c r="G329" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H329" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I329" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J329" s="22"/>
       <c r="K329" s="22"/>
@@ -13135,7 +13126,7 @@
     </row>
     <row r="330" spans="1:14">
       <c r="A330" s="22" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C330" s="22">
         <v>1.19E-6</v>
@@ -13148,13 +13139,13 @@
       </c>
       <c r="F330" s="22"/>
       <c r="G330" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H330" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I330" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J330" s="22"/>
       <c r="K330" s="22"/>
@@ -13164,7 +13155,7 @@
     </row>
     <row r="331" spans="1:14">
       <c r="A331" s="22" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C331" s="22">
         <v>1.9299999999999999E-7</v>
@@ -13177,13 +13168,13 @@
       </c>
       <c r="F331" s="22"/>
       <c r="G331" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H331" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I331" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J331" s="22"/>
       <c r="K331" s="22"/>
@@ -13193,7 +13184,7 @@
     </row>
     <row r="332" spans="1:14">
       <c r="A332" s="22" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C332" s="22">
         <v>3.0400000000000001E-6</v>
@@ -13206,13 +13197,13 @@
       </c>
       <c r="F332" s="22"/>
       <c r="G332" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H332" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I332" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J332" s="22"/>
       <c r="K332" s="22"/>
@@ -13222,7 +13213,7 @@
     </row>
     <row r="333" spans="1:14">
       <c r="A333" s="22" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C333" s="22">
         <v>4.8099999999999997E-6</v>
@@ -13235,13 +13226,13 @@
       </c>
       <c r="F333" s="22"/>
       <c r="G333" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H333" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I333" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J333" s="22"/>
       <c r="K333" s="22"/>
@@ -13251,7 +13242,7 @@
     </row>
     <row r="334" spans="1:14">
       <c r="A334" s="22" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C334" s="22">
         <v>5.94E-5</v>
@@ -13264,13 +13255,13 @@
       </c>
       <c r="F334" s="22"/>
       <c r="G334" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H334" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I334" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J334" s="22"/>
       <c r="K334" s="22"/>
@@ -13280,7 +13271,7 @@
     </row>
     <row r="335" spans="1:14">
       <c r="A335" s="22" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C335" s="22">
         <v>3.3700000000000001E-7</v>
@@ -13293,13 +13284,13 @@
       </c>
       <c r="F335" s="22"/>
       <c r="G335" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H335" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I335" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J335" s="22"/>
       <c r="K335" s="22"/>
@@ -13309,7 +13300,7 @@
     </row>
     <row r="336" spans="1:14">
       <c r="A336" s="22" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C336" s="22">
         <v>1.6800000000000002E-8</v>
@@ -13322,13 +13313,13 @@
       </c>
       <c r="F336" s="22"/>
       <c r="G336" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H336" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I336" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J336" s="22"/>
       <c r="K336" s="22"/>
@@ -13338,7 +13329,7 @@
     </row>
     <row r="337" spans="1:34">
       <c r="A337" s="22" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C337" s="22">
         <v>5.7800000000000001E-7</v>
@@ -13351,13 +13342,13 @@
       </c>
       <c r="F337" s="22"/>
       <c r="G337" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H337" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I337" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J337" s="22"/>
       <c r="K337" s="22"/>
@@ -13367,7 +13358,7 @@
     </row>
     <row r="338" spans="1:34">
       <c r="A338" s="22" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C338" s="22">
         <v>2.1699999999999999E-8</v>
@@ -13380,13 +13371,13 @@
       </c>
       <c r="F338" s="22"/>
       <c r="G338" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H338" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I338" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J338" s="22"/>
       <c r="K338" s="22"/>
@@ -13396,7 +13387,7 @@
     </row>
     <row r="339" spans="1:34">
       <c r="A339" s="22" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C339" s="22">
         <v>3.6099999999999999E-8</v>
@@ -13409,13 +13400,13 @@
       </c>
       <c r="F339" s="22"/>
       <c r="G339" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H339" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I339" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J339" s="22"/>
       <c r="K339" s="22"/>
@@ -13425,7 +13416,7 @@
     </row>
     <row r="340" spans="1:34">
       <c r="A340" s="22" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C340" s="22">
         <v>2.65E-7</v>
@@ -13438,13 +13429,13 @@
       </c>
       <c r="F340" s="22"/>
       <c r="G340" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H340" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I340" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J340" s="22"/>
       <c r="K340" s="22"/>
@@ -13454,7 +13445,7 @@
     </row>
     <row r="341" spans="1:34">
       <c r="A341" s="22" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C341" s="22">
         <v>1.1999999999999999E-7</v>
@@ -13467,13 +13458,13 @@
       </c>
       <c r="F341" s="22"/>
       <c r="G341" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H341" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I341" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J341" s="22"/>
       <c r="K341" s="22"/>
@@ -13483,7 +13474,7 @@
     </row>
     <row r="342" spans="1:34">
       <c r="A342" s="22" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C342" s="22">
         <v>2.6399999999999998E-7</v>
@@ -13496,13 +13487,13 @@
       </c>
       <c r="F342" s="22"/>
       <c r="G342" s="22" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H342" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I342" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J342" s="22"/>
       <c r="K342" s="22"/>
@@ -13531,7 +13522,7 @@
         <v>15</v>
       </c>
       <c r="I343" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J343" s="22"/>
       <c r="K343" s="22"/>
@@ -13560,7 +13551,7 @@
         <v>15</v>
       </c>
       <c r="I344" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J344" s="22"/>
       <c r="K344" s="22"/>
@@ -13589,7 +13580,7 @@
         <v>15</v>
       </c>
       <c r="I345" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J345" s="22"/>
       <c r="K345" s="22"/>
@@ -13599,7 +13590,7 @@
     </row>
     <row r="346" spans="1:34">
       <c r="A346" s="22" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C346" s="22">
         <v>9.7499999999999998E-5</v>
@@ -13618,7 +13609,7 @@
         <v>15</v>
       </c>
       <c r="I346" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J346" s="22"/>
       <c r="K346" s="22"/>
@@ -13628,7 +13619,7 @@
     </row>
     <row r="347" spans="1:34">
       <c r="A347" s="22" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C347" s="22">
         <v>7.5100000000000001E-6</v>
@@ -13647,7 +13638,7 @@
         <v>15</v>
       </c>
       <c r="I347" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J347" s="22"/>
       <c r="K347" s="22"/>
@@ -13657,7 +13648,7 @@
     </row>
     <row r="348" spans="1:34">
       <c r="A348" s="22" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C348" s="22">
         <v>0</v>
@@ -13676,7 +13667,7 @@
         <v>15</v>
       </c>
       <c r="I348" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="J348" s="22"/>
       <c r="K348" s="22"/>
@@ -13740,7 +13731,7 @@
         <v>11</v>
       </c>
       <c r="B351" s="26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C351" s="25"/>
       <c r="D351" s="26"/>
@@ -13916,10 +13907,10 @@
     </row>
     <row r="361" spans="1:34">
       <c r="A361" s="31" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B361" s="22" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C361" s="32">
         <v>1</v>
@@ -14047,7 +14038,7 @@
         <v>11</v>
       </c>
       <c r="B366" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C366" s="25"/>
       <c r="D366" s="26"/>
@@ -14334,7 +14325,7 @@
         <v>11</v>
       </c>
       <c r="B380" s="26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C380" s="25"/>
       <c r="D380" s="26"/>
@@ -14594,7 +14585,7 @@
         <v>11</v>
       </c>
       <c r="B392" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C392" s="25"/>
       <c r="D392" s="26"/>
@@ -15158,7 +15149,7 @@
         <v>11</v>
       </c>
       <c r="B406" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C406" s="25"/>
       <c r="D406" s="26"/>
@@ -15432,7 +15423,7 @@
         <v>1</v>
       </c>
       <c r="B419" s="24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C419" s="25"/>
       <c r="D419" s="26"/>
@@ -15472,7 +15463,7 @@
         <v>11</v>
       </c>
       <c r="B420" s="26" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C420" s="25"/>
       <c r="D420" s="26"/>
@@ -15552,7 +15543,7 @@
         <v>4</v>
       </c>
       <c r="B422" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C422" s="25"/>
       <c r="D422" s="26"/>
@@ -15672,7 +15663,7 @@
         <v>57</v>
       </c>
       <c r="B425" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C425" s="25"/>
       <c r="D425" s="29"/>
@@ -15801,10 +15792,10 @@
     </row>
     <row r="428" spans="1:34">
       <c r="A428" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B428" s="31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C428" s="32">
         <v>1</v>
@@ -15903,10 +15894,10 @@
     </row>
     <row r="430" spans="1:34">
       <c r="A430" s="31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B430" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C430" s="32">
         <v>0</v>
@@ -15953,10 +15944,10 @@
     </row>
     <row r="431" spans="1:34">
       <c r="A431" s="31" t="s">
+        <v>271</v>
+      </c>
+      <c r="B431" s="31" t="s">
         <v>272</v>
-      </c>
-      <c r="B431" s="31" t="s">
-        <v>273</v>
       </c>
       <c r="C431" s="32">
         <v>0</v>
@@ -16003,10 +15994,10 @@
     </row>
     <row r="432" spans="1:34">
       <c r="A432" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="B432" s="31" t="s">
         <v>274</v>
-      </c>
-      <c r="B432" s="31" t="s">
-        <v>275</v>
       </c>
       <c r="C432" s="32">
         <v>1</v>
@@ -16053,10 +16044,10 @@
     </row>
     <row r="433" spans="1:34">
       <c r="A433" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="B433" s="31" t="s">
         <v>278</v>
-      </c>
-      <c r="B433" s="31" t="s">
-        <v>279</v>
       </c>
       <c r="C433" s="32">
         <v>0</v>
@@ -16103,10 +16094,10 @@
     </row>
     <row r="434" spans="1:34">
       <c r="A434" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B434" s="31" t="s">
         <v>280</v>
-      </c>
-      <c r="B434" s="31" t="s">
-        <v>281</v>
       </c>
       <c r="C434" s="32">
         <v>0</v>
@@ -16153,10 +16144,10 @@
     </row>
     <row r="435" spans="1:34">
       <c r="A435" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B435" s="31" t="s">
         <v>282</v>
-      </c>
-      <c r="B435" s="31" t="s">
-        <v>283</v>
       </c>
       <c r="C435" s="32">
         <v>0</v>
@@ -16175,7 +16166,7 @@
         <v>12</v>
       </c>
       <c r="I435" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J435" s="31"/>
       <c r="K435" s="31"/>
@@ -16205,10 +16196,10 @@
     </row>
     <row r="436" spans="1:34">
       <c r="A436" s="31" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B436" s="31" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C436" s="32">
         <v>0</v>
@@ -16294,7 +16285,7 @@
         <v>1</v>
       </c>
       <c r="B438" s="24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C438" s="25"/>
       <c r="D438" s="26"/>
@@ -16334,7 +16325,7 @@
         <v>11</v>
       </c>
       <c r="B439" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C439" s="25"/>
       <c r="D439" s="26"/>
@@ -16414,7 +16405,7 @@
         <v>4</v>
       </c>
       <c r="B441" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C441" s="25"/>
       <c r="D441" s="26"/>
@@ -16534,7 +16525,7 @@
         <v>57</v>
       </c>
       <c r="B444" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C444" s="25"/>
       <c r="D444" s="29"/>
@@ -16663,10 +16654,10 @@
     </row>
     <row r="447" spans="1:34">
       <c r="A447" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="B447" s="31" t="s">
         <v>274</v>
-      </c>
-      <c r="B447" s="31" t="s">
-        <v>275</v>
       </c>
       <c r="C447" s="32">
         <v>1</v>
@@ -16853,7 +16844,7 @@
         <v>11</v>
       </c>
       <c r="B453" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="454" spans="1:34">
@@ -16894,7 +16885,7 @@
       </c>
       <c r="B458"/>
     </row>
-    <row r="459" spans="1:34" ht="15.6">
+    <row r="459" spans="1:34" ht="15.75">
       <c r="A459" s="18" t="s">
         <v>7</v>
       </c>
@@ -17067,7 +17058,7 @@
     </row>
     <row r="467" spans="1:9">
       <c r="A467" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B467" s="13" t="s">
         <v>121</v>
@@ -17250,7 +17241,7 @@
         <v>11</v>
       </c>
       <c r="B477" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="478" spans="1:9">
@@ -17291,7 +17282,7 @@
       </c>
       <c r="B482"/>
     </row>
-    <row r="483" spans="1:9" ht="15.6">
+    <row r="483" spans="1:9" ht="15.75">
       <c r="A483" s="18" t="s">
         <v>7</v>
       </c>
@@ -17464,7 +17455,7 @@
     </row>
     <row r="491" spans="1:9">
       <c r="A491" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B491" s="13" t="s">
         <v>121</v>
@@ -17827,7 +17818,7 @@
         <v>11</v>
       </c>
       <c r="B509" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="510" spans="1:8">
@@ -17868,7 +17859,7 @@
       </c>
       <c r="B514"/>
     </row>
-    <row r="515" spans="1:9" ht="15.6">
+    <row r="515" spans="1:9" ht="15.75">
       <c r="A515" s="18" t="s">
         <v>7</v>
       </c>
@@ -18041,7 +18032,7 @@
     </row>
     <row r="523" spans="1:9">
       <c r="A523" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B523" s="13" t="s">
         <v>121</v>
@@ -18404,7 +18395,7 @@
         <v>11</v>
       </c>
       <c r="B541" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="542" spans="1:8">
@@ -18445,7 +18436,7 @@
       </c>
       <c r="B546"/>
     </row>
-    <row r="547" spans="1:9" ht="15.6">
+    <row r="547" spans="1:9" ht="15.75">
       <c r="A547" s="18" t="s">
         <v>7</v>
       </c>
@@ -18618,7 +18609,7 @@
     </row>
     <row r="555" spans="1:9">
       <c r="A555" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B555" s="13" t="s">
         <v>121</v>
@@ -18981,7 +18972,7 @@
         <v>11</v>
       </c>
       <c r="B573" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="574" spans="1:8">
@@ -19022,7 +19013,7 @@
       </c>
       <c r="B578"/>
     </row>
-    <row r="579" spans="1:9" ht="15.6">
+    <row r="579" spans="1:9" ht="15.75">
       <c r="A579" s="18" t="s">
         <v>7</v>
       </c>
@@ -19195,7 +19186,7 @@
     </row>
     <row r="587" spans="1:9">
       <c r="A587" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B587" s="13" t="s">
         <v>121</v>
@@ -19558,7 +19549,7 @@
         <v>11</v>
       </c>
       <c r="B605" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="606" spans="1:8">
@@ -19599,7 +19590,7 @@
       </c>
       <c r="B610"/>
     </row>
-    <row r="611" spans="1:9" ht="15.6">
+    <row r="611" spans="1:9" ht="15.75">
       <c r="A611" s="18" t="s">
         <v>7</v>
       </c>
@@ -19772,7 +19763,7 @@
     </row>
     <row r="619" spans="1:9">
       <c r="A619" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B619" s="13" t="s">
         <v>121</v>
@@ -19955,7 +19946,7 @@
         <v>11</v>
       </c>
       <c r="B629" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="630" spans="1:9">
@@ -19996,7 +19987,7 @@
       </c>
       <c r="B634"/>
     </row>
-    <row r="635" spans="1:9" ht="15.6">
+    <row r="635" spans="1:9" ht="15.75">
       <c r="A635" s="18" t="s">
         <v>7</v>
       </c>
@@ -20169,7 +20160,7 @@
     </row>
     <row r="643" spans="1:9">
       <c r="A643" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B643" s="13" t="s">
         <v>121</v>
@@ -20532,7 +20523,7 @@
         <v>11</v>
       </c>
       <c r="B661" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="662" spans="1:9">
@@ -20573,7 +20564,7 @@
       </c>
       <c r="B666"/>
     </row>
-    <row r="667" spans="1:9" ht="15.6">
+    <row r="667" spans="1:9" ht="15.75">
       <c r="A667" s="18" t="s">
         <v>7</v>
       </c>
@@ -20746,7 +20737,7 @@
     </row>
     <row r="675" spans="1:9">
       <c r="A675" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B675" s="13" t="s">
         <v>121</v>
@@ -21109,7 +21100,7 @@
         <v>11</v>
       </c>
       <c r="B693" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="694" spans="1:9">
@@ -21150,7 +21141,7 @@
       </c>
       <c r="B698"/>
     </row>
-    <row r="699" spans="1:9" ht="15.6">
+    <row r="699" spans="1:9" ht="15.75">
       <c r="A699" s="18" t="s">
         <v>7</v>
       </c>
@@ -21323,7 +21314,7 @@
     </row>
     <row r="707" spans="1:9">
       <c r="A707" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B707" s="13" t="s">
         <v>121</v>
@@ -21686,7 +21677,7 @@
         <v>11</v>
       </c>
       <c r="B725" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="726" spans="1:9">
@@ -21728,7 +21719,7 @@
       </c>
       <c r="B730"/>
     </row>
-    <row r="731" spans="1:9" ht="15.6">
+    <row r="731" spans="1:9" ht="15.75">
       <c r="A731" s="18" t="s">
         <v>7</v>
       </c>
@@ -21901,7 +21892,7 @@
     </row>
     <row r="739" spans="1:9">
       <c r="A739" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B739" s="13" t="s">
         <v>121</v>
@@ -22264,7 +22255,7 @@
         <v>11</v>
       </c>
       <c r="B757" s="13" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="758" spans="1:21">
@@ -22307,7 +22298,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="763" spans="1:21" ht="15.6">
+    <row r="763" spans="1:21" ht="15.75">
       <c r="A763" s="18" t="s">
         <v>7</v>
       </c>
@@ -22576,10 +22567,10 @@
     </row>
     <row r="770" spans="1:19" s="26" customFormat="1">
       <c r="A770" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B770" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C770" s="45">
         <v>1</v>
@@ -23309,7 +23300,7 @@
         <v>11</v>
       </c>
       <c r="B812" s="31" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="813" spans="1:11" s="26" customFormat="1">
@@ -23417,26 +23408,23 @@
     </row>
     <row r="821" spans="1:9">
       <c r="A821" t="s">
+        <v>479</v>
+      </c>
+      <c r="B821" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="B821" s="31" t="s">
-        <v>260</v>
-      </c>
       <c r="C821" s="46">
-        <v>0.20588960000000001</v>
+        <v>0.1764792</v>
       </c>
       <c r="D821" s="26" t="s">
         <v>35</v>
       </c>
       <c r="E821" s="31"/>
       <c r="G821" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H821" s="31" t="s">
         <v>12</v>
-      </c>
-      <c r="I821" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="822" spans="1:9">
@@ -23459,7 +23447,7 @@
         <v>12</v>
       </c>
       <c r="I822" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="823" spans="1:9">
@@ -23468,7 +23456,7 @@
       </c>
       <c r="B823"/>
       <c r="C823" s="21">
-        <v>9.038187058823539E-4</v>
+        <v>6.366155912253407E-4</v>
       </c>
       <c r="D823" t="s">
         <v>13</v>
@@ -23483,7 +23471,7 @@
         <v>15</v>
       </c>
       <c r="I823" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="824" spans="1:9">
@@ -23492,7 +23480,7 @@
       </c>
       <c r="B824"/>
       <c r="C824" s="21">
-        <v>1.0430494235294118E-2</v>
+        <v>7.346844241170861E-3</v>
       </c>
       <c r="D824" t="s">
         <v>13</v>
@@ -23507,7 +23495,7 @@
         <v>15</v>
       </c>
       <c r="I824" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="825" spans="1:9" s="49" customFormat="1">
@@ -23518,7 +23506,7 @@
         <v>1</v>
       </c>
       <c r="B826" s="43" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C826" s="25"/>
     </row>
@@ -23527,7 +23515,7 @@
         <v>11</v>
       </c>
       <c r="B827" s="31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="828" spans="1:9" s="26" customFormat="1">
@@ -23544,7 +23532,7 @@
         <v>4</v>
       </c>
       <c r="B829" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C829" s="25"/>
     </row>
@@ -23613,10 +23601,10 @@
     </row>
     <row r="835" spans="1:9" s="26" customFormat="1">
       <c r="A835" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B835" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C835" s="45">
         <v>1</v>
@@ -23636,27 +23624,23 @@
     </row>
     <row r="836" spans="1:9">
       <c r="A836" t="s">
+        <v>479</v>
+      </c>
+      <c r="B836" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="B836" s="31" t="s">
-        <v>260</v>
-      </c>
       <c r="C836" s="46">
-        <f>0.00593*35.8</f>
-        <v>0.21229399999999998</v>
+        <v>0.1764792</v>
       </c>
       <c r="D836" s="26" t="s">
         <v>35</v>
       </c>
       <c r="E836" s="31"/>
       <c r="G836" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H836" s="31" t="s">
         <v>12</v>
-      </c>
-      <c r="I836" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="837" spans="1:9">
@@ -23679,7 +23663,7 @@
         <v>12</v>
       </c>
       <c r="I837" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="838" spans="1:9">
@@ -23688,7 +23672,7 @@
       </c>
       <c r="B838"/>
       <c r="C838" s="13">
-        <v>1.0754999999999999E-2</v>
+        <v>7.5754137849407994E-3</v>
       </c>
       <c r="D838" t="s">
         <v>13</v>
@@ -23703,7 +23687,7 @@
         <v>15</v>
       </c>
       <c r="I838" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="839" spans="1:9" s="49" customFormat="1">
@@ -23714,7 +23698,7 @@
         <v>1</v>
       </c>
       <c r="B840" s="43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C840" s="25"/>
       <c r="D840" s="26"/>
@@ -23729,7 +23713,7 @@
         <v>11</v>
       </c>
       <c r="B841" s="31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C841" s="26"/>
       <c r="D841" s="26"/>
@@ -23856,7 +23840,7 @@
     </row>
     <row r="849" spans="1:9">
       <c r="A849" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B849" s="31" t="s">
         <v>99</v>
@@ -23878,12 +23862,12 @@
     </row>
     <row r="850" spans="1:9">
       <c r="A850" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B850" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="C850">
+        <v>287</v>
+      </c>
+      <c r="C850" s="41">
         <v>0.1764792</v>
       </c>
       <c r="D850" s="26" t="s">
@@ -23896,12 +23880,12 @@
         <v>12</v>
       </c>
       <c r="I850" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="851" spans="1:9">
       <c r="A851" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B851" s="13" t="s">
         <v>99</v>
@@ -23921,7 +23905,7 @@
     </row>
     <row r="852" spans="1:9">
       <c r="A852" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B852" s="13" t="s">
         <v>99</v>
@@ -23941,7 +23925,7 @@
     </row>
     <row r="853" spans="1:9">
       <c r="A853" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B853" s="13" t="s">
         <v>99</v>
@@ -23961,7 +23945,7 @@
     </row>
     <row r="854" spans="1:9">
       <c r="A854" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B854" s="13" t="s">
         <v>99</v>
@@ -23981,7 +23965,7 @@
     </row>
     <row r="855" spans="1:9">
       <c r="A855" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B855" s="13" t="s">
         <v>99</v>
@@ -24001,7 +23985,7 @@
     </row>
     <row r="856" spans="1:9">
       <c r="A856" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B856" s="13" t="s">
         <v>99</v>
@@ -24021,7 +24005,7 @@
     </row>
     <row r="857" spans="1:9">
       <c r="A857" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B857" s="13" t="s">
         <v>99</v>
@@ -24044,7 +24028,7 @@
         <v>84</v>
       </c>
       <c r="C858" s="13">
-        <v>9.6000000000000002E-5</v>
+        <v>6.4625669007360007E-5</v>
       </c>
       <c r="D858" s="26" t="s">
         <v>13</v>
@@ -24060,7 +24044,7 @@
         <v>15</v>
       </c>
       <c r="I858" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
     </row>
     <row r="859" spans="1:9">
@@ -24068,7 +24052,7 @@
         <v>32</v>
       </c>
       <c r="C859" s="13">
-        <v>3.435E-4</v>
+        <v>2.3123872191696001E-4</v>
       </c>
       <c r="D859" s="26" t="s">
         <v>13</v>
@@ -24084,15 +24068,15 @@
         <v>15</v>
       </c>
       <c r="I859" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
     </row>
     <row r="860" spans="1:9">
       <c r="A860" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C860" s="13">
-        <v>8.234999999999999E-4</v>
+        <v>5.5436706695375997E-4</v>
       </c>
       <c r="D860" s="26" t="s">
         <v>13</v>
@@ -24108,15 +24092,15 @@
         <v>15</v>
       </c>
       <c r="I860" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
     </row>
     <row r="861" spans="1:9">
       <c r="A861" t="s">
         <v>86</v>
       </c>
-      <c r="C861" s="13">
-        <v>9.9435000000000009E-3</v>
+      <c r="C861" s="57">
+        <v>6.6938056226529602E-3</v>
       </c>
       <c r="D861" s="26" t="s">
         <v>13</v>
@@ -24131,7 +24115,7 @@
         <v>15</v>
       </c>
       <c r="I861" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
     </row>
     <row r="862" spans="1:9">
@@ -24139,7 +24123,7 @@
         <v>142</v>
       </c>
       <c r="C862" s="13">
-        <v>7.5000000000000002E-6</v>
+        <v>5.0488803912000003E-6</v>
       </c>
       <c r="D862" s="26" t="s">
         <v>13</v>
@@ -24155,7 +24139,7 @@
         <v>15</v>
       </c>
       <c r="I862" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
     </row>
     <row r="863" spans="1:9">
@@ -24163,7 +24147,7 @@
         <v>88</v>
       </c>
       <c r="C863" s="13">
-        <v>1.8599999999999999E-4</v>
+        <v>1.2521223370175999E-4</v>
       </c>
       <c r="D863" s="26" t="s">
         <v>13</v>
@@ -24179,7 +24163,7 @@
         <v>15</v>
       </c>
       <c r="I863" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
     </row>
     <row r="864" spans="1:9">
@@ -24198,7 +24182,7 @@
         <v>1</v>
       </c>
       <c r="B865" s="43" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C865" s="25"/>
       <c r="D865" s="26"/>
@@ -24213,7 +24197,7 @@
         <v>11</v>
       </c>
       <c r="B866" s="31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C866" s="26"/>
       <c r="D866" s="26"/>
@@ -24288,7 +24272,7 @@
         <v>57</v>
       </c>
       <c r="B871" s="26" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C871" s="25"/>
       <c r="D871" s="29"/>
@@ -24342,7 +24326,7 @@
     </row>
     <row r="874" spans="1:9">
       <c r="A874" s="31" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B874" s="31" t="s">
         <v>170</v>
@@ -24364,7 +24348,7 @@
     </row>
     <row r="875" spans="1:9">
       <c r="A875" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B875" s="31" t="s">
         <v>170</v>
@@ -24398,7 +24382,7 @@
         <v>1</v>
       </c>
       <c r="B877" s="43" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C877" s="25"/>
       <c r="D877" s="26"/>
@@ -24413,7 +24397,7 @@
         <v>11</v>
       </c>
       <c r="B878" s="31" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C878" s="26"/>
       <c r="D878" s="26"/>
@@ -24443,7 +24427,7 @@
         <v>4</v>
       </c>
       <c r="B880" s="31" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C880" s="25"/>
       <c r="D880" s="26"/>
@@ -24473,7 +24457,7 @@
         <v>6</v>
       </c>
       <c r="B882" s="51" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C882" s="25"/>
       <c r="D882" s="29"/>
@@ -24540,16 +24524,16 @@
     </row>
     <row r="886" spans="1:10">
       <c r="A886" s="43" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B886" s="31" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C886" s="26">
         <v>1</v>
       </c>
       <c r="D886" s="26" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F886" s="24"/>
       <c r="G886" s="31" t="s">
@@ -24571,12 +24555,12 @@
       <c r="H887" s="49"/>
       <c r="I887" s="49"/>
     </row>
-    <row r="888" spans="1:10" ht="15.6">
+    <row r="888" spans="1:10" ht="15.75">
       <c r="A888" s="18" t="s">
         <v>1</v>
       </c>
       <c r="B888" s="43" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="889" spans="1:10">
@@ -24603,7 +24587,7 @@
         <v>4</v>
       </c>
       <c r="B891" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F891" s="13"/>
       <c r="J891" s="56"/>
@@ -24633,7 +24617,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="895" spans="1:10" ht="15.6">
+    <row r="895" spans="1:10" ht="15.75">
       <c r="A895" s="18" t="s">
         <v>7</v>
       </c>
@@ -24689,7 +24673,7 @@
         <v>15</v>
       </c>
       <c r="I897" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="898" spans="1:9">
@@ -24713,7 +24697,7 @@
         <v>15</v>
       </c>
       <c r="I898" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="899" spans="1:9">
@@ -24737,7 +24721,7 @@
         <v>15</v>
       </c>
       <c r="I899" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="900" spans="1:9">
@@ -24766,7 +24750,7 @@
     </row>
     <row r="901" spans="1:9">
       <c r="A901" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B901"/>
       <c r="C901">
@@ -24811,7 +24795,7 @@
     </row>
     <row r="903" spans="1:9">
       <c r="A903" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B903"/>
       <c r="C903">
@@ -24835,10 +24819,10 @@
     </row>
     <row r="904" spans="1:9">
       <c r="A904" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B904" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C904">
         <v>1</v>
@@ -24858,7 +24842,7 @@
     </row>
     <row r="905" spans="1:9">
       <c r="A905" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B905"/>
       <c r="C905">
@@ -24874,12 +24858,12 @@
         <v>12</v>
       </c>
       <c r="I905" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="906" spans="1:9">
       <c r="A906" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B906"/>
       <c r="C906">
@@ -24895,15 +24879,15 @@
         <v>12</v>
       </c>
       <c r="I906" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="907" spans="1:9">
       <c r="A907" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B907" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C907">
         <v>9.5E-4</v>
@@ -24918,15 +24902,15 @@
         <v>12</v>
       </c>
       <c r="I907" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="908" spans="1:9">
       <c r="A908" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B908" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C908">
         <v>1.7399999999999999E-5</v>
@@ -24941,15 +24925,15 @@
         <v>12</v>
       </c>
       <c r="I908" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="909" spans="1:9">
       <c r="A909" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B909" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C909">
         <v>5.7600000000000001E-4</v>
@@ -24964,15 +24948,15 @@
         <v>12</v>
       </c>
       <c r="I909" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="910" spans="1:9">
       <c r="A910" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B910" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C910">
         <v>1.1600000000000001E-11</v>
@@ -24987,7 +24971,7 @@
         <v>12</v>
       </c>
       <c r="I910" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="911" spans="1:9">
@@ -25010,7 +24994,7 @@
         <v>12</v>
       </c>
       <c r="I911" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="912" spans="1:9">
@@ -25033,7 +25017,7 @@
         <v>12</v>
       </c>
       <c r="I912" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="913" spans="1:9">
@@ -25056,15 +25040,15 @@
         <v>12</v>
       </c>
       <c r="I913" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="914" spans="1:9">
       <c r="A914" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B914" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C914">
         <v>0.1020326</v>
@@ -25079,12 +25063,12 @@
         <v>12</v>
       </c>
       <c r="I914" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="915" spans="1:9">
       <c r="A915" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B915" t="s">
         <v>33</v>
@@ -25096,7 +25080,7 @@
         <v>19</v>
       </c>
       <c r="G915" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H915" t="s">
         <v>12</v>
@@ -25107,10 +25091,10 @@
     </row>
     <row r="916" spans="1:9">
       <c r="A916" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B916" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C916">
         <v>1.1600000000000001E-11</v>
@@ -25119,21 +25103,21 @@
         <v>13</v>
       </c>
       <c r="G916" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H916" t="s">
         <v>12</v>
       </c>
       <c r="I916" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="917" spans="1:9">
       <c r="A917" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B917" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C917">
         <v>-2.0200000000000001E-3</v>
@@ -25148,15 +25132,15 @@
         <v>12</v>
       </c>
       <c r="I917" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="918" spans="1:9">
       <c r="A918" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B918" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C918">
         <v>-1.1600000000000001E-11</v>
@@ -25171,15 +25155,15 @@
         <v>12</v>
       </c>
       <c r="I918" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="919" spans="1:9">
       <c r="A919" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B919" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C919">
         <v>-1.1600000000000001E-11</v>
@@ -25194,15 +25178,15 @@
         <v>12</v>
       </c>
       <c r="I919" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="920" spans="1:9">
       <c r="A920" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B920" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C920">
         <v>-5.63E-5</v>
@@ -25217,15 +25201,15 @@
         <v>12</v>
       </c>
       <c r="I920" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="921" spans="1:9">
       <c r="A921" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B921" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C921">
         <v>-9.4499999999999998E-4</v>
@@ -25240,15 +25224,15 @@
         <v>12</v>
       </c>
       <c r="I921" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="922" spans="1:9">
       <c r="A922" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B922" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C922">
         <v>6.28E-6</v>
@@ -25263,15 +25247,15 @@
         <v>12</v>
       </c>
       <c r="I922" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="923" spans="1:9">
       <c r="A923" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B923" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C923" s="13">
         <v>0.15468000000000001</v>

--- a/inventories/lci-Tr2050.xlsx
+++ b/inventories/lci-Tr2050.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie-my.sharepoint.com/personal/db6421_engie_com/Documents/Documents/GitHub/ADEME_scenarios_premise_gas/inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1759" documentId="13_ncr:1_{6A9A1C53-53B4-4DAF-B82F-70FF83AECA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D0D3474-BBD2-4870-A7ED-E2183A0A0CA7}"/>
+  <xr:revisionPtr revIDLastSave="1812" documentId="13_ncr:1_{6A9A1C53-53B4-4DAF-B82F-70FF83AECA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5960DED-332F-4C3B-BA33-6F8DDDE6C464}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3934" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4115" uniqueCount="484">
   <si>
     <t>Database</t>
   </si>
@@ -1307,9 +1307,6 @@
     <t>Production of refused  derived fuels. It is modelled as a waste to gasification</t>
   </si>
   <si>
-    <t>kg</t>
-  </si>
-  <si>
     <t>RDF, waste</t>
   </si>
   <si>
@@ -1476,6 +1473,21 @@
   </si>
   <si>
     <t>heat production, biomethane, at boiler condensing modulating &lt;100kW</t>
+  </si>
+  <si>
+    <t>Refused derived fuels (not adapted to their LHV)</t>
+  </si>
+  <si>
+    <t>synthetic natural gas from RDF, 70 bar, at plant</t>
+  </si>
+  <si>
+    <t>Synthetic natural gas from RDF, 70 bar, at plant</t>
+  </si>
+  <si>
+    <t>Considered 36% of fossil C-content in refused derived fuels (ADEME Transition 2050 scenarios)</t>
+  </si>
+  <si>
+    <t>refused derived fuels</t>
   </si>
 </sst>
 </file>
@@ -1999,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH923"/>
+  <dimension ref="A1:AH960"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="73.140625" customWidth="1"/>
@@ -11455,7 +11467,7 @@
         <v>57</v>
       </c>
       <c r="B272" s="31" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C272" s="22"/>
       <c r="D272" s="22"/>
@@ -23408,7 +23420,7 @@
     </row>
     <row r="821" spans="1:9">
       <c r="A821" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B821" s="31" t="s">
         <v>259</v>
@@ -23624,7 +23636,7 @@
     </row>
     <row r="836" spans="1:9">
       <c r="A836" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B836" s="31" t="s">
         <v>259</v>
@@ -24044,7 +24056,7 @@
         <v>15</v>
       </c>
       <c r="I858" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="859" spans="1:9">
@@ -24068,7 +24080,7 @@
         <v>15</v>
       </c>
       <c r="I859" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="860" spans="1:9">
@@ -24092,7 +24104,7 @@
         <v>15</v>
       </c>
       <c r="I860" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="861" spans="1:9">
@@ -24115,7 +24127,7 @@
         <v>15</v>
       </c>
       <c r="I861" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="862" spans="1:9">
@@ -24139,7 +24151,7 @@
         <v>15</v>
       </c>
       <c r="I862" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="863" spans="1:9">
@@ -24163,7 +24175,7 @@
         <v>15</v>
       </c>
       <c r="I863" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="864" spans="1:9">
@@ -24427,7 +24439,7 @@
         <v>4</v>
       </c>
       <c r="B880" s="31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C880" s="25"/>
       <c r="D880" s="26"/>
@@ -24456,8 +24468,8 @@
       <c r="A882" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B882" s="51" t="s">
-        <v>423</v>
+      <c r="B882" t="s">
+        <v>13</v>
       </c>
       <c r="C882" s="25"/>
       <c r="D882" s="29"/>
@@ -24523,17 +24535,17 @@
       </c>
     </row>
     <row r="886" spans="1:10">
-      <c r="A886" s="43" t="s">
+      <c r="A886" s="31" t="s">
         <v>421</v>
       </c>
       <c r="B886" s="31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C886" s="26">
         <v>1</v>
       </c>
       <c r="D886" s="26" t="s">
-        <v>423</v>
+        <v>13</v>
       </c>
       <c r="F886" s="24"/>
       <c r="G886" s="31" t="s">
@@ -24560,7 +24572,7 @@
         <v>1</v>
       </c>
       <c r="B888" s="43" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="889" spans="1:10">
@@ -24587,7 +24599,7 @@
         <v>4</v>
       </c>
       <c r="B891" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F891" s="13"/>
       <c r="J891" s="56"/>
@@ -24673,7 +24685,7 @@
         <v>15</v>
       </c>
       <c r="I897" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="898" spans="1:9">
@@ -24697,7 +24709,7 @@
         <v>15</v>
       </c>
       <c r="I898" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="899" spans="1:9">
@@ -24721,7 +24733,7 @@
         <v>15</v>
       </c>
       <c r="I899" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="900" spans="1:9">
@@ -24750,7 +24762,7 @@
     </row>
     <row r="901" spans="1:9">
       <c r="A901" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B901"/>
       <c r="C901">
@@ -24795,7 +24807,7 @@
     </row>
     <row r="903" spans="1:9">
       <c r="A903" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B903"/>
       <c r="C903">
@@ -24819,10 +24831,10 @@
     </row>
     <row r="904" spans="1:9">
       <c r="A904" t="s">
+        <v>425</v>
+      </c>
+      <c r="B904" t="s">
         <v>426</v>
-      </c>
-      <c r="B904" t="s">
-        <v>427</v>
       </c>
       <c r="C904">
         <v>1</v>
@@ -24842,7 +24854,7 @@
     </row>
     <row r="905" spans="1:9">
       <c r="A905" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B905"/>
       <c r="C905">
@@ -24858,12 +24870,12 @@
         <v>12</v>
       </c>
       <c r="I905" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="906" spans="1:9">
       <c r="A906" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B906"/>
       <c r="C906">
@@ -24879,15 +24891,15 @@
         <v>12</v>
       </c>
       <c r="I906" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="907" spans="1:9">
       <c r="A907" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B907" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C907">
         <v>9.5E-4</v>
@@ -24902,15 +24914,15 @@
         <v>12</v>
       </c>
       <c r="I907" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="908" spans="1:9">
       <c r="A908" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B908" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C908">
         <v>1.7399999999999999E-5</v>
@@ -24925,15 +24937,15 @@
         <v>12</v>
       </c>
       <c r="I908" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="909" spans="1:9">
       <c r="A909" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B909" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C909">
         <v>5.7600000000000001E-4</v>
@@ -24948,15 +24960,15 @@
         <v>12</v>
       </c>
       <c r="I909" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="910" spans="1:9">
       <c r="A910" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B910" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C910">
         <v>1.1600000000000001E-11</v>
@@ -24971,7 +24983,7 @@
         <v>12</v>
       </c>
       <c r="I910" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="911" spans="1:9">
@@ -24994,7 +25006,7 @@
         <v>12</v>
       </c>
       <c r="I911" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="912" spans="1:9">
@@ -25017,10 +25029,10 @@
         <v>12</v>
       </c>
       <c r="I912" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="913" spans="1:9">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="913" spans="1:10">
       <c r="A913" t="s">
         <v>156</v>
       </c>
@@ -25040,15 +25052,15 @@
         <v>12</v>
       </c>
       <c r="I913" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="914" spans="1:10">
+      <c r="A914" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="914" spans="1:9">
-      <c r="A914" t="s">
-        <v>451</v>
-      </c>
       <c r="B914" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C914">
         <v>0.1020326</v>
@@ -25063,10 +25075,10 @@
         <v>12</v>
       </c>
       <c r="I914" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="915" spans="1:9">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="915" spans="1:10">
       <c r="A915" t="s">
         <v>354</v>
       </c>
@@ -25080,7 +25092,7 @@
         <v>19</v>
       </c>
       <c r="G915" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H915" t="s">
         <v>12</v>
@@ -25089,12 +25101,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="916" spans="1:9">
+    <row r="916" spans="1:10">
       <c r="A916" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B916" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C916">
         <v>1.1600000000000001E-11</v>
@@ -25103,21 +25115,21 @@
         <v>13</v>
       </c>
       <c r="G916" t="s">
+        <v>454</v>
+      </c>
+      <c r="H916" t="s">
+        <v>12</v>
+      </c>
+      <c r="I916" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="917" spans="1:10">
+      <c r="A917" t="s">
         <v>455</v>
       </c>
-      <c r="H916" t="s">
-        <v>12</v>
-      </c>
-      <c r="I916" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="917" spans="1:9">
-      <c r="A917" t="s">
-        <v>456</v>
-      </c>
       <c r="B917" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C917">
         <v>-2.0200000000000001E-3</v>
@@ -25132,15 +25144,15 @@
         <v>12</v>
       </c>
       <c r="I917" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="918" spans="1:9">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="918" spans="1:10">
       <c r="A918" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B918" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C918">
         <v>-1.1600000000000001E-11</v>
@@ -25155,15 +25167,15 @@
         <v>12</v>
       </c>
       <c r="I918" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="919" spans="1:9">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="919" spans="1:10">
       <c r="A919" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B919" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C919">
         <v>-1.1600000000000001E-11</v>
@@ -25178,15 +25190,15 @@
         <v>12</v>
       </c>
       <c r="I919" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="920" spans="1:9">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="920" spans="1:10">
       <c r="A920" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B920" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C920">
         <v>-5.63E-5</v>
@@ -25201,15 +25213,15 @@
         <v>12</v>
       </c>
       <c r="I920" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="921" spans="1:9">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="921" spans="1:10">
       <c r="A921" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B921" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C921">
         <v>-9.4499999999999998E-4</v>
@@ -25224,15 +25236,15 @@
         <v>12</v>
       </c>
       <c r="I921" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="922" spans="1:9">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="922" spans="1:10">
       <c r="A922" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B922" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C922">
         <v>6.28E-6</v>
@@ -25247,15 +25259,15 @@
         <v>12</v>
       </c>
       <c r="I922" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="923" spans="1:9">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="923" spans="1:10">
       <c r="A923" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B923" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C923" s="13">
         <v>0.15468000000000001</v>
@@ -25268,6 +25280,735 @@
       </c>
       <c r="H923" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="924" spans="1:10">
+      <c r="A924" s="49"/>
+      <c r="B924" s="50"/>
+      <c r="C924" s="49"/>
+      <c r="D924" s="49"/>
+      <c r="E924" s="49"/>
+      <c r="F924" s="49"/>
+      <c r="G924" s="49"/>
+      <c r="H924" s="49"/>
+      <c r="I924" s="49"/>
+    </row>
+    <row r="925" spans="1:10" ht="15.75">
+      <c r="A925" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B925" s="43" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="926" spans="1:10">
+      <c r="A926" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B926" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="H926" s="55"/>
+    </row>
+    <row r="927" spans="1:10">
+      <c r="A927" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B927">
+        <v>1</v>
+      </c>
+      <c r="F927" s="13"/>
+      <c r="H927" s="13"/>
+    </row>
+    <row r="928" spans="1:10">
+      <c r="A928" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B928" t="s">
+        <v>480</v>
+      </c>
+      <c r="F928" s="13"/>
+      <c r="J928" s="56"/>
+    </row>
+    <row r="929" spans="1:9">
+      <c r="A929" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B929" t="s">
+        <v>59</v>
+      </c>
+      <c r="F929" s="20"/>
+    </row>
+    <row r="930" spans="1:9">
+      <c r="A930" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B930" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="931" spans="1:9">
+      <c r="A931" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B931" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9" ht="15.75">
+      <c r="A932" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B932"/>
+    </row>
+    <row r="933" spans="1:9">
+      <c r="A933" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B933" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C933" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D933" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E933" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F933" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G933" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H933" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="I933" s="27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9">
+      <c r="A934" t="s">
+        <v>138</v>
+      </c>
+      <c r="B934"/>
+      <c r="C934">
+        <f>0.152-C935</f>
+        <v>9.7280000000000005E-2</v>
+      </c>
+      <c r="D934" t="s">
+        <v>13</v>
+      </c>
+      <c r="E934" t="s">
+        <v>83</v>
+      </c>
+      <c r="F934" t="s">
+        <v>25</v>
+      </c>
+      <c r="H934" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9">
+      <c r="A935" t="s">
+        <v>32</v>
+      </c>
+      <c r="B935"/>
+      <c r="C935">
+        <f>0.152*0.36</f>
+        <v>5.4719999999999998E-2</v>
+      </c>
+      <c r="D935" t="s">
+        <v>13</v>
+      </c>
+      <c r="E935" t="s">
+        <v>83</v>
+      </c>
+      <c r="F935" t="s">
+        <v>25</v>
+      </c>
+      <c r="H935" t="s">
+        <v>15</v>
+      </c>
+      <c r="I935" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9">
+      <c r="A936" t="s">
+        <v>138</v>
+      </c>
+      <c r="B936"/>
+      <c r="C936">
+        <v>1.1100000000000001E-3</v>
+      </c>
+      <c r="D936" t="s">
+        <v>13</v>
+      </c>
+      <c r="E936" t="s">
+        <v>83</v>
+      </c>
+      <c r="F936" t="s">
+        <v>25</v>
+      </c>
+      <c r="H936" t="s">
+        <v>15</v>
+      </c>
+      <c r="I936" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9">
+      <c r="A937" t="s">
+        <v>138</v>
+      </c>
+      <c r="B937"/>
+      <c r="C937">
+        <v>1.57E-3</v>
+      </c>
+      <c r="D937" t="s">
+        <v>13</v>
+      </c>
+      <c r="E937" t="s">
+        <v>83</v>
+      </c>
+      <c r="F937" t="s">
+        <v>25</v>
+      </c>
+      <c r="H937" t="s">
+        <v>15</v>
+      </c>
+      <c r="I937" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9">
+      <c r="A938" t="s">
+        <v>140</v>
+      </c>
+      <c r="B938"/>
+      <c r="C938">
+        <v>8.1500000000000002E-5</v>
+      </c>
+      <c r="D938" t="s">
+        <v>13</v>
+      </c>
+      <c r="E938" t="s">
+        <v>83</v>
+      </c>
+      <c r="F938" t="s">
+        <v>109</v>
+      </c>
+      <c r="H938" t="s">
+        <v>15</v>
+      </c>
+      <c r="I938" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9">
+      <c r="A939" t="s">
+        <v>431</v>
+      </c>
+      <c r="B939"/>
+      <c r="C939">
+        <v>8.9400000000000008E-6</v>
+      </c>
+      <c r="D939" t="s">
+        <v>13</v>
+      </c>
+      <c r="E939" t="s">
+        <v>83</v>
+      </c>
+      <c r="F939" t="s">
+        <v>109</v>
+      </c>
+      <c r="H939" t="s">
+        <v>15</v>
+      </c>
+      <c r="I939" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9">
+      <c r="A940" t="s">
+        <v>87</v>
+      </c>
+      <c r="B940"/>
+      <c r="C940">
+        <v>4.6900000000000002E-5</v>
+      </c>
+      <c r="D940" t="s">
+        <v>13</v>
+      </c>
+      <c r="E940" t="s">
+        <v>83</v>
+      </c>
+      <c r="F940" t="s">
+        <v>109</v>
+      </c>
+      <c r="H940" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9">
+      <c r="A941" t="s">
+        <v>432</v>
+      </c>
+      <c r="B941"/>
+      <c r="C941">
+        <v>1.2899999999999999E-6</v>
+      </c>
+      <c r="D941" t="s">
+        <v>13</v>
+      </c>
+      <c r="E941" t="s">
+        <v>83</v>
+      </c>
+      <c r="F941" t="s">
+        <v>109</v>
+      </c>
+      <c r="H941" t="s">
+        <v>15</v>
+      </c>
+      <c r="I941" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9">
+      <c r="A942" t="s">
+        <v>481</v>
+      </c>
+      <c r="B942" t="s">
+        <v>480</v>
+      </c>
+      <c r="C942">
+        <v>1</v>
+      </c>
+      <c r="D942" t="s">
+        <v>35</v>
+      </c>
+      <c r="G942" t="s">
+        <v>28</v>
+      </c>
+      <c r="H942" t="s">
+        <v>18</v>
+      </c>
+      <c r="I942" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9">
+      <c r="A943" t="s">
+        <v>433</v>
+      </c>
+      <c r="B943"/>
+      <c r="C943">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="D943" t="s">
+        <v>35</v>
+      </c>
+      <c r="G943" t="s">
+        <v>36</v>
+      </c>
+      <c r="H943" t="s">
+        <v>12</v>
+      </c>
+      <c r="I943" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9">
+      <c r="A944" t="s">
+        <v>435</v>
+      </c>
+      <c r="B944"/>
+      <c r="C944">
+        <v>4.7200000000000002E-11</v>
+      </c>
+      <c r="D944" t="s">
+        <v>6</v>
+      </c>
+      <c r="G944" t="s">
+        <v>36</v>
+      </c>
+      <c r="H944" t="s">
+        <v>12</v>
+      </c>
+      <c r="I944" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9">
+      <c r="A945" t="s">
+        <v>437</v>
+      </c>
+      <c r="B945" t="s">
+        <v>439</v>
+      </c>
+      <c r="C945">
+        <v>9.5E-4</v>
+      </c>
+      <c r="D945" t="s">
+        <v>13</v>
+      </c>
+      <c r="G945" t="s">
+        <v>36</v>
+      </c>
+      <c r="H945" t="s">
+        <v>12</v>
+      </c>
+      <c r="I945" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9">
+      <c r="A946" t="s">
+        <v>440</v>
+      </c>
+      <c r="B946" t="s">
+        <v>442</v>
+      </c>
+      <c r="C946">
+        <v>1.7399999999999999E-5</v>
+      </c>
+      <c r="D946" t="s">
+        <v>35</v>
+      </c>
+      <c r="G946" t="s">
+        <v>26</v>
+      </c>
+      <c r="H946" t="s">
+        <v>12</v>
+      </c>
+      <c r="I946" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9">
+      <c r="A947" t="s">
+        <v>443</v>
+      </c>
+      <c r="B947" t="s">
+        <v>445</v>
+      </c>
+      <c r="C947">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="D947" t="s">
+        <v>13</v>
+      </c>
+      <c r="G947" t="s">
+        <v>26</v>
+      </c>
+      <c r="H947" t="s">
+        <v>12</v>
+      </c>
+      <c r="I947" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9">
+      <c r="A948" t="s">
+        <v>473</v>
+      </c>
+      <c r="B948" t="s">
+        <v>472</v>
+      </c>
+      <c r="C948">
+        <v>1.1600000000000001E-11</v>
+      </c>
+      <c r="D948" t="s">
+        <v>13</v>
+      </c>
+      <c r="G948" t="s">
+        <v>134</v>
+      </c>
+      <c r="H948" t="s">
+        <v>12</v>
+      </c>
+      <c r="I948" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9">
+      <c r="A949" t="s">
+        <v>186</v>
+      </c>
+      <c r="B949" t="s">
+        <v>187</v>
+      </c>
+      <c r="C949">
+        <v>5.3499999999999999E-4</v>
+      </c>
+      <c r="D949" t="s">
+        <v>13</v>
+      </c>
+      <c r="G949" t="s">
+        <v>96</v>
+      </c>
+      <c r="H949" t="s">
+        <v>12</v>
+      </c>
+      <c r="I949" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9">
+      <c r="A950" t="s">
+        <v>156</v>
+      </c>
+      <c r="B950" t="s">
+        <v>157</v>
+      </c>
+      <c r="C950">
+        <v>5.6100000000000004E-3</v>
+      </c>
+      <c r="D950" t="s">
+        <v>158</v>
+      </c>
+      <c r="G950" t="s">
+        <v>36</v>
+      </c>
+      <c r="H950" t="s">
+        <v>12</v>
+      </c>
+      <c r="I950" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9">
+      <c r="A951" t="s">
+        <v>156</v>
+      </c>
+      <c r="B951" t="s">
+        <v>157</v>
+      </c>
+      <c r="C951">
+        <v>2.7399999999999999E-4</v>
+      </c>
+      <c r="D951" t="s">
+        <v>158</v>
+      </c>
+      <c r="G951" t="s">
+        <v>36</v>
+      </c>
+      <c r="H951" t="s">
+        <v>12</v>
+      </c>
+      <c r="I951" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9">
+      <c r="A952" s="31" t="s">
+        <v>483</v>
+      </c>
+      <c r="B952" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="C952">
+        <v>0.1020326</v>
+      </c>
+      <c r="D952" t="s">
+        <v>13</v>
+      </c>
+      <c r="G952" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="H952" t="s">
+        <v>12</v>
+      </c>
+      <c r="I952" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9">
+      <c r="A953" t="s">
+        <v>354</v>
+      </c>
+      <c r="B953" t="s">
+        <v>33</v>
+      </c>
+      <c r="C953">
+        <v>1.77E-2</v>
+      </c>
+      <c r="D953" t="s">
+        <v>19</v>
+      </c>
+      <c r="G953" t="s">
+        <v>453</v>
+      </c>
+      <c r="H953" t="s">
+        <v>12</v>
+      </c>
+      <c r="I953" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9">
+      <c r="A954" t="s">
+        <v>476</v>
+      </c>
+      <c r="B954" t="s">
+        <v>475</v>
+      </c>
+      <c r="C954">
+        <v>1.1600000000000001E-11</v>
+      </c>
+      <c r="D954" t="s">
+        <v>13</v>
+      </c>
+      <c r="G954" t="s">
+        <v>454</v>
+      </c>
+      <c r="H954" t="s">
+        <v>12</v>
+      </c>
+      <c r="I954" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9">
+      <c r="A955" t="s">
+        <v>455</v>
+      </c>
+      <c r="B955" t="s">
+        <v>457</v>
+      </c>
+      <c r="C955">
+        <v>-2.0200000000000001E-3</v>
+      </c>
+      <c r="D955" t="s">
+        <v>13</v>
+      </c>
+      <c r="G955" t="s">
+        <v>26</v>
+      </c>
+      <c r="H955" t="s">
+        <v>12</v>
+      </c>
+      <c r="I955" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9">
+      <c r="A956" t="s">
+        <v>458</v>
+      </c>
+      <c r="B956" t="s">
+        <v>460</v>
+      </c>
+      <c r="C956">
+        <v>-1.1600000000000001E-11</v>
+      </c>
+      <c r="D956" t="s">
+        <v>13</v>
+      </c>
+      <c r="G956" t="s">
+        <v>26</v>
+      </c>
+      <c r="H956" t="s">
+        <v>12</v>
+      </c>
+      <c r="I956" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9">
+      <c r="A957" t="s">
+        <v>461</v>
+      </c>
+      <c r="B957" t="s">
+        <v>463</v>
+      </c>
+      <c r="C957">
+        <v>-1.1600000000000001E-11</v>
+      </c>
+      <c r="D957" t="s">
+        <v>13</v>
+      </c>
+      <c r="G957" t="s">
+        <v>26</v>
+      </c>
+      <c r="H957" t="s">
+        <v>12</v>
+      </c>
+      <c r="I957" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9">
+      <c r="A958" t="s">
+        <v>464</v>
+      </c>
+      <c r="B958" t="s">
+        <v>466</v>
+      </c>
+      <c r="C958">
+        <v>-5.63E-5</v>
+      </c>
+      <c r="D958" t="s">
+        <v>13</v>
+      </c>
+      <c r="G958" t="s">
+        <v>26</v>
+      </c>
+      <c r="H958" t="s">
+        <v>12</v>
+      </c>
+      <c r="I958" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9">
+      <c r="A959" t="s">
+        <v>467</v>
+      </c>
+      <c r="B959" t="s">
+        <v>469</v>
+      </c>
+      <c r="C959">
+        <v>-9.4499999999999998E-4</v>
+      </c>
+      <c r="D959" t="s">
+        <v>13</v>
+      </c>
+      <c r="G959" t="s">
+        <v>26</v>
+      </c>
+      <c r="H959" t="s">
+        <v>12</v>
+      </c>
+      <c r="I959" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9">
+      <c r="A960" t="s">
+        <v>474</v>
+      </c>
+      <c r="B960" t="s">
+        <v>471</v>
+      </c>
+      <c r="C960">
+        <v>6.28E-6</v>
+      </c>
+      <c r="D960" t="s">
+        <v>13</v>
+      </c>
+      <c r="G960" t="s">
+        <v>96</v>
+      </c>
+      <c r="H960" t="s">
+        <v>12</v>
+      </c>
+      <c r="I960" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>
